--- a/docs/PracticeLab_Chart_Composition_Taxonomy.xlsx
+++ b/docs/PracticeLab_Chart_Composition_Taxonomy.xlsx
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +73,16 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B23A33"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -139,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -224,6 +234,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -591,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -759,50 +781,72 @@
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>What the targets are and are not</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="39" customHeight="1">
+          <t>The four populations are separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>A target is a proportion of a pool, not a forecast of what production will yield. Where the two disagree the pool is wrong, not the sheet: a pool that drifts toward whatever charts were easy to find teaches whatever those charts happened to contain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
+          <t>ED Facility, ED Profee, ED Single Path and E/M are four distinct chart populations, confirmed on 15 October 2026. The same clinical encounter coded for the facility, coded professionally, and coded single-path produces three different charts, and none of them sits in the E/M pool. Their pools therefore add rather than overlap, and the E/M topic list holding no ED setting is deliberate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Rounding is per topic, so the sum of targets can differ from the pool by a chart or two. Each sheet shows the variance rather than hiding it, and the pool is the authority.</t>
+          <t>The consequence for sourcing is the part worth saying out loud: four populations means four separate pulls, not one pull classified four ways. A chart cannot be filed under an ED Facility topic and an ED Profee topic at once, and reusing one encounter across two pools would put the same documentation in front of a coder twice under two different names.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="52" customHeight="1">
+          <t>What the targets are and are not</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="39" customHeight="1">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Seven specialties. IP-DRG, ED Facility, E/M and SDS carry HC baseline pools. ED Profee, Surgery and ED Single Path each carry a pool set on 15 October 2026 (400, 300 and 300) rather than one derived in the HC model. Denials/Edits and Ancillary are deferred — their HC pools and coverage matrices stand, and a topic layer for them is the obvious next addition.</t>
+          <t>A target is a proportion of a pool, not a forecast of what production will yield. Where the two disagree the pool is wrong, not the sheet: a pool that drifts toward whatever charts were easy to find teaches whatever those charts happened to contain.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
+          <t>Rounding is per topic, so the sum of targets can differ from the pool by a chart or two. Each sheet shows the variance rather than hiding it, and the pool is the authority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Seven specialties. IP-DRG, ED Facility, E/M and SDS carry HC baseline pools. ED Profee, Surgery and ED Single Path each carry a pool set on 15 October 2026 (400, 300 and 300) rather than one derived in the HC model. Denials/Edits and Ancillary are deferred — their HC pools and coverage matrices stand, and a topic layer for them is the obvious next addition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t>Open questions that need a decision before this is final are on the Open Decisions sheet. They are listed rather than resolved because each changes a number somebody else owns.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B5:C5"/>
@@ -810,6 +854,8 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A2:C2"/>
@@ -824,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1746,26 +1792,34 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="26" customHeight="1">
+    <row r="46" ht="39" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>Severity on IP-DRG and Method on E/M are cross-cutting dimensions: a chart has a CC/MCC status and an MDM-or-time basis whatever its topic. They are checked across the pool, not decomposed per topic, which is why the topic sheets carry one dimension each.</t>
+          <t>ED Facility, ED Profee and ED Single Path are three separate populations, not three views of one. The same encounter coded for the facility, coded professionally and coded single-path is three different charts; none of them belongs in the E/M pool, which is why the E/M dimension here has no ED setting. Confirmed 15 October 2026.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
+          <t>Severity on IP-DRG and Method on E/M are cross-cutting dimensions: a chart has a CC/MCC status and an MDM-or-time basis whatever its topic. They are checked across the pool, not decomposed per topic, which is why the topic sheets carry one dimension each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
           <t>Where a target percentage here changes, the matching band row on the topic sheet and its child weights must change together. The band row's check cell is what tells you they have come apart.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A48:F48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2087,26 +2141,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open decisions</t>
+          <t>Decisions</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Each one changes a number somebody else owns, so they are listed rather than resolved. Nothing on the topic sheets depends on them being settled first.</t>
+          <t>Settled ones first, with what was decided. The open ones each change a number somebody else owns, so they are listed rather than resolved — nothing on the topic sheets depends on them being settled first.</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2178,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>What is at stake</t>
+          <t>What is at stake, or what was decided</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -2131,64 +2186,84 @@
           <t>Owner</t>
         </is>
       </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="24" t="n">
+      <c r="A5" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>Add ED Profee, Surgery and ED Single Path to the HC model</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>Pools of 400, 300 and 300 were set here, outside the HC model. None of them has a +10% buffer calculation, a per-batch average, a batch count or a build-hour line. That is 1,000 charts the HC Specialty Grid, Chart Pool, FTE Demand and FTE Summary sheets do not know about — at HC's own build rates roughly 1,500 to 2,250 hours, close to a further FTE. Until they are added, the team size in that model is understated.</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Whoever owns the HC model</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="24" t="n">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>ED Facility, ED Profee, ED Single Path and E/M are four separate chart populations</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>Confirmed: an ED encounter coded for the facility, the same encounter coded professionally, and a single-path encounter are three different charts, and none of them belongs in the E/M pool. So the pools of 704, 400, 300 and 413 do not overlap and nothing is double-counted — but sourcing has to pull four distinct populations, and the E/M pool holding no ED setting is correct rather than an oversight.</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>Confirmed by the user</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Settled 2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>Confirm ED Profee and ED Single Path do not double-count ED Facility</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>One ED encounter can be coded facility-only, profee-only or single-path. Three pools of 704, 400 and 300 assume three distinct chart populations. If the same encounters are being counted twice, the ED requirement is overstated by up to 700 charts; if they genuinely are distinct, sourcing has to pull three times from the same production stream.</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>PL Trainer, ED specialties</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>E/M keeps no ED-setting share</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Follows from the above. ED E/M sits in ED Profee, the E/M topic list deliberately holds no ED setting, and the HC E/M pool of 413 is not oversized by it.</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>Confirmed by the user</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>Settled 2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="77" customHeight="1">
       <c r="A7" s="24" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>Decide whether E/M keeps an ED-setting share</t>
+          <t>Add ED Profee, Surgery and ED Single Path to the HC model</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>ED E/M now sits in ED Profee, so the E/M topic list deliberately holds no ED setting. If the HC E/M pool of 413 was sized including ED visits, it is now oversized by that share and the ED Profee 400 partly duplicates it.</t>
+          <t>Pools of 400, 300 and 300 were set here, outside the HC model. None of them has a +10% buffer calculation, a per-batch average, a batch count or a build-hour line. That is 1,000 charts the HC Specialty Grid, Chart Pool, FTE Demand and FTE Summary sheets do not know about — at HC's own build rates roughly 1,500 to 2,250 hours, close to a further FTE. Until they are added, the team size in that model is understated.</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>PL Trainer, E/M</t>
+          <t>Whoever owns the HC model</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2211,8 +2286,13 @@
           <t>PL Trainer plus QR</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="24" t="n">
         <v>5</v>
       </c>
@@ -2231,8 +2311,13 @@
           <t>PL Trainer plus Compliance for X2</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="24" t="n">
         <v>6</v>
       </c>
@@ -2251,8 +2336,13 @@
           <t>PL Trainer plus the platform team</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="24" t="n">
         <v>7</v>
       </c>
@@ -2269,6 +2359,11 @@
       <c r="D11" s="11" t="inlineStr">
         <is>
           <t>PL Trainer</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2291,11 +2386,16 @@
           <t>PL Trainer, at the first refresh</t>
         </is>
       </c>
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/PracticeLab_Chart_Composition_Taxonomy.xlsx
+++ b/docs/PracticeLab_Chart_Composition_Taxonomy.xlsx
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,12 +76,22 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="002E7D32"/>
+      <color rgb="00B23A33"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00B23A33"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -149,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -211,6 +221,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,10 +261,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -613,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -778,64 +794,76 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="21" ht="52" customHeight="1">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Build priority</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>P1, P2 or P3 per topic, in a column of its own, because priority and volume are different questions. The weight says how many charts a topic should hold once the pool is complete; the priority says which topics are sourced and built before it is. IP-DRG leads with the OB and newborn block across both medical and surgical DRGs, then GI, respiratory and cardiovascular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>The four populations are separate</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>ED Facility, ED Profee, ED Single Path and E/M are four distinct chart populations, confirmed on 15 October 2026. The same clinical encounter coded for the facility, coded professionally, and coded single-path produces three different charts, and none of them sits in the E/M pool. Their pools therefore add rather than overlap, and the E/M topic list holding no ED setting is deliberate.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
+          <t>ED Facility, ED Profee, ED Single Path and E/M are four distinct chart populations, confirmed on 15 October 2026. The same clinical encounter coded for the facility, coded professionally, and coded single-path produces three different charts, and none of them sits in the E/M pool. Their pools therefore add rather than overlap, and the E/M topic list holding no ED setting is deliberate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>The consequence for sourcing is the part worth saying out loud: four populations means four separate pulls, not one pull classified four ways. A chart cannot be filed under an ED Facility topic and an ED Profee topic at once, and reusing one encounter across two pools would put the same documentation in front of a coder twice under two different names.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>What the targets are and are not</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="39" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="39" customHeight="1">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>A target is a proportion of a pool, not a forecast of what production will yield. Where the two disagree the pool is wrong, not the sheet: a pool that drifts toward whatever charts were easy to find teaches whatever those charts happened to contain.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="B28" s="4" t="inlineStr">
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Rounding is per topic, so the sum of targets can differ from the pool by a chart or two. Each sheet shows the variance rather than hiding it, and the pool is the authority.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="52" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="52" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Seven specialties. IP-DRG, ED Facility, E/M and SDS carry HC baseline pools. ED Profee, Surgery and ED Single Path each carry a pool set on 15 October 2026 (400, 300 and 300) rather than one derived in the HC model. Denials/Edits and Ancillary are deferred — their HC pools and coverage matrices stand, and a topic layer for them is the obvious next addition.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Open questions that need a decision before this is final are on the Open Decisions sheet. They are listed rather than resolved because each changes a number somebody else owns.</t>
         </is>
@@ -846,17 +874,17 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
@@ -944,10 +972,10 @@
           <t>Medical DRGs (top client volume)</t>
         </is>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="32" t="n">
         <v>381</v>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -964,10 +992,10 @@
           <t>Surgical DRGs (top client volume)</t>
         </is>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="31" t="n">
         <v>0.45</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="32" t="n">
         <v>312</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -988,10 +1016,10 @@
           <t>Without CC/MCC</t>
         </is>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="32" t="n">
         <v>208</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1008,10 +1036,10 @@
           <t>With CC</t>
         </is>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="32" t="n">
         <v>243</v>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -1028,10 +1056,10 @@
           <t>With MCC</t>
         </is>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="32" t="n">
         <v>243</v>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1041,20 +1069,20 @@
       </c>
     </row>
     <row r="10" ht="33" customHeight="1">
-      <c r="A10" s="30" t="inlineStr"/>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr"/>
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Must include</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>POA indicators · principal diagnosis sequencing · ICD-10-PCS procedures · query opportunities</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>Carried from HC Chart Selection section 6. Every one of these appears in the elements column of at least one IP-DRG topic.</t>
         </is>
@@ -1076,10 +1104,10 @@
           <t>Levels 1–2</t>
         </is>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="32" t="n">
         <v>141</v>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1096,10 +1124,10 @@
           <t>Level 3</t>
         </is>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="32" t="n">
         <v>211</v>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -1116,10 +1144,10 @@
           <t>Level 4</t>
         </is>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="32" t="n">
         <v>211</v>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1136,10 +1164,10 @@
           <t>Level 5 / critical care</t>
         </is>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="32" t="n">
         <v>141</v>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -1149,20 +1177,20 @@
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="30" t="inlineStr"/>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr"/>
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Must include</t>
         </is>
       </c>
-      <c r="C15" s="30" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>Injuries · infusions and injections · ED procedures · observation</t>
         </is>
       </c>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="D15" s="33" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>Carried from HC Chart Selection section 6</t>
         </is>
@@ -1184,10 +1212,10 @@
           <t>Low (levels 2–3)</t>
         </is>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="32" t="n">
         <v>145</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -1204,10 +1232,10 @@
           <t>Moderate (level 4)</t>
         </is>
       </c>
-      <c r="D17" s="28" t="n">
+      <c r="D17" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="32" t="n">
         <v>165</v>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1224,10 +1252,10 @@
           <t>High (level 5)</t>
         </is>
       </c>
-      <c r="D18" s="28" t="n">
+      <c r="D18" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="32" t="n">
         <v>103</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -1248,10 +1276,10 @@
           <t>MDM-based</t>
         </is>
       </c>
-      <c r="D19" s="28" t="n">
+      <c r="D19" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="32" t="n">
         <v>330</v>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -1268,10 +1296,10 @@
           <t>Time-based</t>
         </is>
       </c>
-      <c r="D20" s="28" t="n">
+      <c r="D20" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="32" t="n">
         <v>83</v>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -1281,20 +1309,20 @@
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="30" t="inlineStr"/>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr"/>
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Must include</t>
         </is>
       </c>
-      <c r="C21" s="30" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>New versus established · office versus hospital · modifier 25 · split and shared visits</t>
         </is>
       </c>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="31" t="n"/>
-      <c r="F21" s="32" t="inlineStr">
+      <c r="D21" s="33" t="n"/>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="35" t="inlineStr">
         <is>
           <t>Carried from HC Chart Selection section 6</t>
         </is>
@@ -1316,10 +1344,10 @@
           <t>Orthopaedics</t>
         </is>
       </c>
-      <c r="D22" s="28" t="n">
+      <c r="D22" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="32" t="n">
         <v>33</v>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -1336,10 +1364,10 @@
           <t>GI / endoscopy</t>
         </is>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D23" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="32" t="n">
         <v>33</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -1356,10 +1384,10 @@
           <t>Ophthalmology</t>
         </is>
       </c>
-      <c r="D24" s="28" t="n">
+      <c r="D24" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="32" t="n">
         <v>20</v>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -1376,10 +1404,10 @@
           <t>Pain management</t>
         </is>
       </c>
-      <c r="D25" s="28" t="n">
+      <c r="D25" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="32" t="n">
         <v>20</v>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -1396,10 +1424,10 @@
           <t>Other surgical</t>
         </is>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D26" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="32" t="n">
         <v>26</v>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -1409,20 +1437,20 @@
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="30" t="inlineStr"/>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr"/>
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Must include</t>
         </is>
       </c>
-      <c r="C27" s="30" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>Modifiers (bilateral, distinct procedure) · implants and devices</t>
         </is>
       </c>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="D27" s="33" t="n"/>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="35" t="inlineStr">
         <is>
           <t>Carried from HC Chart Selection section 6</t>
         </is>
@@ -1444,10 +1472,10 @@
           <t>Low acuity (99281 / 99282)</t>
         </is>
       </c>
-      <c r="D28" s="28" t="n">
+      <c r="D28" s="31" t="n">
         <v>0.08</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="32" t="n">
         <v>32</v>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -1464,10 +1492,10 @@
           <t>Moderate (99283)</t>
         </is>
       </c>
-      <c r="D29" s="28" t="n">
+      <c r="D29" s="31" t="n">
         <v>0.18</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="32" t="n">
         <v>72</v>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -1484,10 +1512,10 @@
           <t>Level 4 (99284)</t>
         </is>
       </c>
-      <c r="D30" s="28" t="n">
+      <c r="D30" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="32" t="n">
         <v>80</v>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -1504,10 +1532,10 @@
           <t>Level 5 (99285)</t>
         </is>
       </c>
-      <c r="D31" s="28" t="n">
+      <c r="D31" s="31" t="n">
         <v>0.24</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="32" t="n">
         <v>96</v>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -1524,10 +1552,10 @@
           <t>Critical care (99291 / 99292)</t>
         </is>
       </c>
-      <c r="D32" s="28" t="n">
+      <c r="D32" s="31" t="n">
         <v>0.12</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="32" t="n">
         <v>48</v>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -1544,10 +1572,10 @@
           <t>Cross-cutting (procedures, observation, split/shared)</t>
         </is>
       </c>
-      <c r="D33" s="28" t="n">
+      <c r="D33" s="31" t="n">
         <v>0.18</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="32" t="n">
         <v>72</v>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -1557,20 +1585,20 @@
       </c>
     </row>
     <row r="34" ht="33" customHeight="1">
-      <c r="A34" s="30" t="inlineStr"/>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="A34" s="33" t="inlineStr"/>
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>Must include</t>
         </is>
       </c>
-      <c r="C34" s="30" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
         <is>
           <t>Modifier 25 · the 99285 versus 99291 boundary · split and shared documentation</t>
         </is>
       </c>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="32" t="inlineStr">
+      <c r="D34" s="33" t="n"/>
+      <c r="E34" s="34" t="n"/>
+      <c r="F34" s="35" t="inlineStr">
         <is>
           <t>Not in the HC model — set 2026-10-15 with this workbook. The boundary charts only plant if AnswerKey.cc_boundary is set to borderline.</t>
         </is>
@@ -1592,10 +1620,10 @@
           <t>High-volume service lines (general, ortho, CT/vascular, neuro, gynae)</t>
         </is>
       </c>
-      <c r="D35" s="28" t="n">
+      <c r="D35" s="31" t="n">
         <v>0.64</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="32" t="n">
         <v>192</v>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -1612,10 +1640,10 @@
           <t>Specialty and cross-cutting</t>
         </is>
       </c>
-      <c r="D36" s="28" t="n">
+      <c r="D36" s="31" t="n">
         <v>0.36</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="32" t="n">
         <v>108</v>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -1625,20 +1653,20 @@
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="30" t="inlineStr"/>
-      <c r="B37" s="30" t="inlineStr">
+      <c r="A37" s="33" t="inlineStr"/>
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>Must include</t>
         </is>
       </c>
-      <c r="C37" s="30" t="inlineStr">
+      <c r="C37" s="33" t="inlineStr">
         <is>
           <t>Global period and staged procedure modifiers · co-surgeon and assistant modifiers · laterality</t>
         </is>
       </c>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="D37" s="33" t="n"/>
+      <c r="E37" s="34" t="n"/>
+      <c r="F37" s="35" t="inlineStr">
         <is>
           <t>Not in the HC model — set 2026-10-15 with this workbook</t>
         </is>
@@ -1660,10 +1688,10 @@
           <t>Low acuity</t>
         </is>
       </c>
-      <c r="D38" s="28" t="n">
+      <c r="D38" s="31" t="n">
         <v>0.08</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="32" t="n">
         <v>24</v>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -1680,10 +1708,10 @@
           <t>Moderate (level 3)</t>
         </is>
       </c>
-      <c r="D39" s="28" t="n">
+      <c r="D39" s="31" t="n">
         <v>0.18</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="32" t="n">
         <v>54</v>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -1700,10 +1728,10 @@
           <t>Level 4</t>
         </is>
       </c>
-      <c r="D40" s="28" t="n">
+      <c r="D40" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="32" t="n">
         <v>60</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -1720,10 +1748,10 @@
           <t>Level 5</t>
         </is>
       </c>
-      <c r="D41" s="28" t="n">
+      <c r="D41" s="31" t="n">
         <v>0.22</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="32" t="n">
         <v>66</v>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -1740,10 +1768,10 @@
           <t>Critical care</t>
         </is>
       </c>
-      <c r="D42" s="28" t="n">
+      <c r="D42" s="31" t="n">
         <v>0.12</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="32" t="n">
         <v>36</v>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -1760,10 +1788,10 @@
           <t>Cross-cutting</t>
         </is>
       </c>
-      <c r="D43" s="28" t="n">
+      <c r="D43" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="32" t="n">
         <v>60</v>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -1773,20 +1801,20 @@
       </c>
     </row>
     <row r="44" ht="33" customHeight="1">
-      <c r="A44" s="30" t="inlineStr"/>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="A44" s="33" t="inlineStr"/>
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>Must include</t>
         </is>
       </c>
-      <c r="C44" s="30" t="inlineStr">
+      <c r="C44" s="33" t="inlineStr">
         <is>
           <t>Both level determinations on one record · legitimate divergence between them · modifier 25</t>
         </is>
       </c>
-      <c r="D44" s="30" t="n"/>
-      <c r="E44" s="31" t="n"/>
-      <c r="F44" s="32" t="inlineStr">
+      <c r="D44" s="33" t="n"/>
+      <c r="E44" s="34" t="n"/>
+      <c r="F44" s="35" t="inlineStr">
         <is>
           <t>Not in the HC model — set 2026-10-15 with this workbook. Divergence is the reason single path is a specialty and not a view of the other two ED pools.</t>
         </is>
@@ -1882,7 +1910,7 @@
           <t>Topic ID</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Yes — new</t>
         </is>
@@ -1904,7 +1932,7 @@
           <t>Specialty and coverage category</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1926,7 +1954,7 @@
           <t>Difficulty tier</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1948,7 +1976,7 @@
           <t>Learning objective(s)</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1970,7 +1998,7 @@
           <t>Sourcing channel</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1992,7 +2020,7 @@
           <t>Source type and client</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2014,7 +2042,7 @@
           <t>Guideline / code-set version</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2036,7 +2064,7 @@
           <t>Build and validation dates</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2058,7 +2086,7 @@
           <t>Usage count</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2080,7 +2108,7 @@
           <t>Answer key presence</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -2102,7 +2130,7 @@
           <t>Authored error version(s)</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -2193,50 +2221,50 @@
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="34" t="n">
+      <c r="A5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>ED Facility, ED Profee, ED Single Path and E/M are four separate chart populations</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>Confirmed: an ED encounter coded for the facility, the same encounter coded professionally, and a single-path encounter are three different charts, and none of them belongs in the E/M pool. So the pools of 704, 400, 300 and 413 do not overlap and nothing is double-counted — but sourcing has to pull four distinct populations, and the E/M pool holding no ED setting is correct rather than an oversight.</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>Confirmed by the user</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="39" t="inlineStr">
         <is>
           <t>Settled 2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t>E/M keeps no ED-setting share</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>Follows from the above. ED E/M sits in ED Profee, the E/M topic list deliberately holds no ED setting, and the HC E/M pool of 413 is not oversized by it.</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Confirmed by the user</t>
         </is>
       </c>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>Settled 2026-10-15</t>
         </is>
@@ -2261,7 +2289,7 @@
           <t>Whoever owns the HC model</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2286,7 +2314,7 @@
           <t>PL Trainer plus QR</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2303,7 +2331,7 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>IPD-09 (mental health), EDF-11 (behavioural health) and IPD-19 (transplant) are narrowed by exclusion X2 or by case rarity. Each needs a stated floor below which it is reported as constrained rather than chased, so a gap report does not show a permanent red against a topic nobody can fill.</t>
+          <t>IPD-13 (mental health), EDF-11 (behavioural health), IPD-16 (obstetric surgical) and IPD-24 (transplant) are narrowed by exclusion X2 or by case rarity. Each needs a stated floor below which it is reported as constrained rather than chased, so a gap report does not show a permanent red against a topic nobody can fill.</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -2311,7 +2339,7 @@
           <t>PL Trainer plus Compliance for X2</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2336,7 +2364,7 @@
           <t>PL Trainer plus the platform team</t>
         </is>
       </c>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2361,7 +2389,7 @@
           <t>PL Trainer</t>
         </is>
       </c>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2386,7 +2414,7 @@
           <t>PL Trainer, at the first refresh</t>
         </is>
       </c>
-      <c r="E12" s="37" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2918,7 +2946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2928,10 +2956,11 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2957,7 +2986,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>COUNTA(A5:A26)-2</f>
+        <f>COUNTA(A5:A31)-2</f>
         <v/>
       </c>
       <c r="E2" s="17" t="inlineStr">
@@ -2966,7 +2995,7 @@
         </is>
       </c>
       <c r="F2" s="18">
-        <f>SUM(G5:G26)</f>
+        <f>SUM(G5:G31)</f>
         <v/>
       </c>
       <c r="G2" s="17" t="inlineStr">
@@ -3026,22 +3055,28 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
+          <t>Build
+priority</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
           <t>Difficulty
 skew</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Primary sourcing
 channel</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Key elements the chart must exercise</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3054,11 +3089,11 @@
         </is>
       </c>
       <c r="F5" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$26,"Medical DRGs",$F$5:$F$26),6)=0.55,"OK — topics sum to the 55% parent","CHECK — topics do not sum to the 55% parent")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
+        <f>IF(ROUND(SUMIF($B$5:$B$31,"Medical DRGs",$F$5:$F$31),6)=0.55,"OK — topics sum to the 55% parent","CHECK — topics do not sum to the 55% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
           <t>IPD-01</t>
@@ -3071,48 +3106,53 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>Respiratory — pneumonia, COPD exacerbation, respiratory failure</t>
+          <t>Vaginal delivery and complications of labour</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>Admissions where the principal diagnosis is respiratory and no OR procedure drives the DRG. Includes acute-on-chronic respiratory failure and the ventilator-hours boundary.</t>
+          <t>Delivery admissions grouping medical: vaginal and assisted delivery, complications of labour, and the maternal record only.</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Thoracotomy and tracheostomy cases — they group surgical (IPD-16)</t>
+          <t>Caesarean delivery — IPD-15; the newborn record — IPD-02</t>
         </is>
       </c>
       <c r="F6" s="23" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="G6" s="24">
         <f>ROUND(F6*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t>Moderate-led</t>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>P1 — build first</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t>C1 High error rate</t>
+          <t>Complex-led</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>Principal diagnosis selection, pneumonia organism specificity, CC/MCC capture, POA, ventilator hours</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>Sequencing respiratory failure against the underlying condition is the most disputed PDx call in this specialty. Carry charts in both directions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1">
+          <t>C6 Customer escalations</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>Principal diagnosis for a delivery admission, Z3A gestational weeks, outcome-of-delivery code, PCS delivery root operation, CC/MCC capture</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>The PDx for a delivery admission is the complication, not the delivery — the error that keeps recurring. Vaginal delivery groups MEDICAL and caesarean groups SURGICAL, so OB sits on both sides of the 55/45 split and must be sourced against both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="21" t="inlineStr">
         <is>
           <t>IPD-02</t>
@@ -3125,48 +3165,53 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>Sepsis, severe sepsis and septic shock</t>
+          <t>Normal newborn and newborn with condition</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>Sepsis as principal or secondary, with and without organ dysfunction. Includes the localised-infection-versus-sepsis judgement and post-procedural sepsis.</t>
+          <t>The newborn record: normal newborn, newborn with a condition identified after birth, and the birth-weight and gestational-age axes that drive grouping.</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Newborn sepsis — IPD-10</t>
+          <t>The maternal record — IPD-01 or IPD-15</t>
         </is>
       </c>
       <c r="F7" s="23" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="G7" s="24">
         <f>ROUND(F7*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>Complex-led</t>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>P1 — build first</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
+          <t>Moderate-led</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>Sepsis sequencing, severe sepsis with organ dysfunction, R65.2x, POA, query opportunity, MCC capture</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>Highest-yield topic for query practice (HC use case 07). Charts with a resolved query are preferred; unresolved ones are excluded by X3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>Birth weight, gestational age, newborn condition coding, POA on a newborn record, liveborn versus condition sequencing</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>Mother and newborn records are linked; HC rule R3 requires PHI scrubbed from both before either is used. Birth weight is entered in grams and is the single most consequential value on the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
         <is>
           <t>IPD-03</t>
@@ -3179,44 +3224,49 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>Circulatory medical — heart failure, AMI, arrhythmia</t>
+          <t>Neonatal and NICU admissions</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>Medical cardiac admissions. Heart failure type and acuity, AMI type 1 versus type 2, atrial fibrillation.</t>
+          <t>Prematurity, low birth weight, respiratory distress of the newborn, and neonatal admissions whose DRG turns on weight bands and procedures.</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>CABG, valve, PCI and EP procedures — IPD-12</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G8" s="24">
         <f>ROUND(F8*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H8" s="22" t="inlineStr">
-        <is>
-          <t>Moderate-led</t>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t>P1 — build first</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
-          <t>C5 DRGV trending PCS / DRG</t>
+          <t>Complex-led</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
         <is>
-          <t>Heart failure specificity, AMI type, CC/MCC capture, PDx sequencing when cardiac and respiratory both present</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>Type 2 MI versus demand ischaemia is a current trending error area; refresh from the DRGV report each cycle.</t>
+          <t>C2 High dollar value</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>Birth-weight band boundaries, prematurity coding, ventilator hours on a neonate, POA, MCC capture</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>The weight bands are hard boundaries: a hundred grams moves the DRG. High dollar value and high error rate at once.</t>
         </is>
       </c>
     </row>
@@ -3233,44 +3283,49 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>Nervous system — CVA, TIA, intracranial haemorrhage</t>
+          <t>Antepartum and postpartum medical admissions</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>Acute neurological admissions coded medically, including thrombolytic administration and residual-deficit codes.</t>
+          <t>Maternal admissions that are not the delivery: hyperemesis, pre-eclampsia, preterm labour not delivered, and postpartum complications managed medically.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Craniotomy, shunt and spine decompression — IPD-14</t>
+          <t>Postpartum surgical procedures — IPD-16</t>
         </is>
       </c>
       <c r="F9" s="23" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G9" s="24">
         <f>ROUND(F9*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>P1 — build first</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
-        <is>
-          <t>C2 High dollar value</t>
-        </is>
-      </c>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>CVA site and laterality, late effect versus acute, thrombolytic status Z92.82, POA, functional deficit capture</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>Z92.82 affects the DRG and is routinely missed when the thrombolytic was given at a transferring facility.</t>
+          <t>C1 High error rate</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>Trimester characters, delivered versus not delivered, postpartum period rules, PDx selection, Z3A</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>The not-delivered admissions are where the trimester character and the delivered/undelivered distinction go wrong.</t>
         </is>
       </c>
     </row>
@@ -3287,48 +3342,49 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>Kidney and urinary — AKI, CKD, UTI</t>
+          <t>Digestive medical — GI bleed, pancreatitis, obstruction</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>Renal admissions with no OR procedure. Includes AKI on CKD, the AKI-versus-dehydration call, and dialysis dependence.</t>
+          <t>Medical GI admissions: GI haemorrhage with and without a stated site, pancreatitis aetiology, obstruction managed conservatively.</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Dialysis access creation and nephrectomy — IPD-15</t>
+          <t>Bowel resection, cholecystectomy and hernia repair — IPD-17</t>
         </is>
       </c>
       <c r="F10" s="23" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G10" s="24">
         <f>ROUND(F10*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
-        <is>
-          <t>AKI versus CKD staging, N17/N18 combination, CC/MCC capture, POA</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>AKI is a CC and is often documented only as a lab trend; a strong query topic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="33" customHeight="1">
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>Bleeding site specificity, aetiology linkage, blood transfusion capture, CC/MCC, PDx sequencing</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="21" t="inlineStr">
         <is>
           <t>IPD-06</t>
@@ -3341,44 +3397,53 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>Digestive medical — GI bleed, pancreatitis, obstruction</t>
+          <t>Respiratory — pneumonia, COPD exacerbation, respiratory failure</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>Medical GI admissions: GI haemorrhage with and without a stated site, pancreatitis aetiology, obstruction managed conservatively.</t>
+          <t>Admissions where the principal diagnosis is respiratory and no OR procedure drives the DRG. Includes acute-on-chronic respiratory failure and the ventilator-hours boundary.</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Bowel resection, cholecystectomy and hernia repair — IPD-13</t>
+          <t>Thoracotomy and tracheostomy cases — IPD-19</t>
         </is>
       </c>
       <c r="F11" s="23" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G11" s="24">
         <f>ROUND(F11*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>C8 Foundation</t>
-        </is>
-      </c>
       <c r="J11" s="22" t="inlineStr">
         <is>
-          <t>Bleeding site specificity, aetiology linkage, blood transfusion capture, CC/MCC</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="33" customHeight="1">
+          <t>C1 High error rate</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>Principal diagnosis selection, pneumonia organism specificity, CC/MCC capture, POA, ventilator hours</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>Sequencing respiratory failure against the underlying condition is the most disputed PDx call in this specialty. Carry charts in both directions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
         <is>
           <t>IPD-07</t>
@@ -3391,44 +3456,49 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>Endocrine and metabolic — DKA, malnutrition, electrolyte disorders</t>
+          <t>Circulatory medical — heart failure, AMI, arrhythmia</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>Diabetic emergencies, severe protein-calorie malnutrition, and significant electrolyte disturbance as principal or as the MCC.</t>
+          <t>Medical cardiac admissions. Heart failure type and acuity, AMI type 1 versus type 2, atrial fibrillation.</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CABG, valve, PCI and EP procedures — IPD-18</t>
         </is>
       </c>
       <c r="F12" s="23" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G12" s="24">
         <f>ROUND(F12*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H12" s="22" t="inlineStr">
-        <is>
-          <t>Complex-led</t>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>C1 High error rate</t>
+          <t>Moderate-led</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
         <is>
-          <t>Diabetes with complication linkage, malnutrition severity and clinical criteria, MCC capture, POA</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>Severe malnutrition is a high-value MCC and the most commonly denied on audit; the chart must carry the clinical criteria, not just the dietitian note.</t>
+          <t>C5 DRGV trending PCS / DRG</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>Heart failure specificity, AMI type, CC/MCC capture, PDx sequencing when cardiac and respiratory both present</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>Type 2 MI versus demand ischaemia is a current trending error area; refresh from the DRGV report each cycle.</t>
         </is>
       </c>
     </row>
@@ -3445,44 +3515,49 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>Haematology and oncology — medical admissions</t>
+          <t>Sepsis, severe sepsis and septic shock</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>Neutropenia, anaemia requiring transfusion, sickle-cell crisis, and admissions for a complication of a malignancy.</t>
+          <t>Sepsis as principal or secondary, with and without organ dysfunction. Includes the localised-infection-versus-sepsis judgement and post-procedural sepsis.</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Admissions for chemotherapy administration alone — out of scope this cycle</t>
+          <t>Newborn sepsis — IPD-02 or IPD-03</t>
         </is>
       </c>
       <c r="F13" s="23" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G13" s="24">
         <f>ROUND(F13*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
-        <is>
-          <t>C6 Customer escalations</t>
-        </is>
-      </c>
       <c r="J13" s="22" t="inlineStr">
         <is>
-          <t>Neoplasm versus complication sequencing, primary versus secondary site, admission-for-treatment rules, anaemia in neoplastic disease</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>Sequencing an admission for a complication of cancer against the cancer itself is a recurring escalation topic.</t>
+          <t>C1 High error rate</t>
+        </is>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>Sepsis sequencing, severe sepsis with organ dysfunction, R65.2x, POA, query opportunity, MCC capture</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>Highest-yield topic for query practice (HC use case 07). Charts with a resolved query are preferred; unresolved ones are excluded by X3.</t>
         </is>
       </c>
     </row>
@@ -3499,44 +3574,49 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>Mental health and substance use</t>
+          <t>Nervous system medical — CVA, TIA, intracranial haemorrhage</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>Psychiatric and substance-withdrawal admissions where the full record is available for training use.</t>
+          <t>Acute neurological admissions coded medically, including thrombolytic administration and residual-deficit codes.</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Anything under 42 CFR Part 2 or client-restricted — removed entirely by X2</t>
+          <t>Craniotomy, shunt and spine decompression — IPD-21</t>
         </is>
       </c>
       <c r="F14" s="23" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G14" s="24">
         <f>ROUND(F14*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H14" s="22" t="inlineStr">
-        <is>
-          <t>Basic-led</t>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>C8 Foundation</t>
+          <t>Complex-led</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
         <is>
-          <t>Substance use versus abuse versus dependence, withdrawal with complication, psychiatric PDx selection</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>Sourcing is narrow by design: X2 removes most candidates. If eligible supply is not there, report it as a constrained topic rather than forcing the target.</t>
+          <t>C2 High dollar value</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>CVA site and laterality, late effect versus acute, thrombolytic status Z92.82, POA, functional deficit capture</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>Z92.82 affects the DRG and is routinely missed when the thrombolytic was given at a transferring facility.</t>
         </is>
       </c>
     </row>
@@ -3553,323 +3633,357 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>Newborn and neonate</t>
+          <t>Kidney and urinary — AKI, CKD, UTI</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>Normal newborn, newborn with condition, and neonatal admissions. Birth-weight and gestational-age driven grouping.</t>
+          <t>Renal admissions with no OR procedure. Includes AKI on CKD, the AKI-versus-dehydration call, and dialysis dependence.</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Maternal delivery records — IPD-17</t>
+          <t>Dialysis access creation and nephrectomy — IPD-22</t>
         </is>
       </c>
       <c r="F15" s="23" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G15" s="24">
         <f>ROUND(F15*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>C6 Customer escalations</t>
-        </is>
-      </c>
       <c r="J15" s="22" t="inlineStr">
         <is>
-          <t>Birth weight, gestational age, newborn condition coding, POA on a newborn record</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>Mother and newborn records are linked; HC rule R3 requires PHI scrubbed from both before either is used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>SURGICAL DRGS  —  HC Coverage Matrix parent: 45%</t>
-        </is>
-      </c>
-      <c r="F16" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$26,"Surgical DRGs",$F$5:$F$26),6)=0.45,"OK — topics sum to the 45% parent","CHECK — topics do not sum to the 45% parent")</f>
-        <v/>
+          <t>C1 High error rate</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>AKI versus CKD staging, N17/N18 combination, CC/MCC capture, POA</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>AKI is a CC and is often documented only as a lab trend; a strong query topic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="33" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>IPD-11</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Medical DRGs</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Endocrine and metabolic — DKA, malnutrition, electrolyte disorders</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Diabetic emergencies, severe protein-calorie malnutrition, and significant electrolyte disturbance as principal or as the MCC.</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G16" s="24">
+        <f>ROUND(F16*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>Complex-led</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>C1 High error rate</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>Diabetes with complication linkage, malnutrition severity and clinical criteria, MCC capture, POA</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>Severe malnutrition is a high-value MCC and the most commonly denied on audit; the chart must carry the clinical criteria, not just the dietitian note.</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="33" customHeight="1">
       <c r="A17" s="21" t="inlineStr">
         <is>
-          <t>IPD-11</t>
+          <t>IPD-12</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>Surgical DRGs</t>
+          <t>Medical DRGs</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>Musculoskeletal — joint replacement, spinal fusion, fracture fixation</t>
+          <t>Haematology and oncology — medical admissions</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>Elective and traumatic MSK surgery requiring admission. Approach and device-value axes of the PCS code, fusion level counts.</t>
+          <t>Neutropenia, anaemia requiring transfusion, sickle-cell crisis, and admissions for a complication of a malignancy.</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Same-day orthopaedic procedures — SDS-01 to SDS-03</t>
+          <t>Admissions for chemotherapy administration alone — out of scope this cycle</t>
         </is>
       </c>
       <c r="F17" s="23" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="G17" s="24">
         <f>ROUND(F17*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>Moderate-led</t>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
         <is>
-          <t>C5 DRGV trending PCS / DRG</t>
+          <t>Complex-led</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
         <is>
-          <t>PCS root operation and device character, fusion levels and approach, bilateral procedures, POA on post-operative conditions</t>
-        </is>
-      </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
-          <t>Highest-volume surgical family and the best place to train PCS character selection. Carries the device-value character the auditor module plants against.</t>
+          <t>C6 Customer escalations</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>Neoplasm versus complication sequencing, primary versus secondary site, admission-for-treatment rules, anaemia in neoplastic disease</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>Sequencing an admission for a complication of cancer against the cancer itself is a recurring escalation topic.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="33" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>IPD-12</t>
+          <t>IPD-13</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>Surgical DRGs</t>
+          <t>Medical DRGs</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>Cardiovascular surgical — CABG, valve, PCI, EP procedures</t>
+          <t>Mental health and substance use</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>Open and percutaneous cardiac procedures, including multi-vessel PCI with differing stent counts and intraoperative conversion.</t>
+          <t>Psychiatric and substance-withdrawal admissions where the full record is available for training use.</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Diagnostic catheterisation with no intervention — out of scope this cycle</t>
+          <t>Anything under 42 CFR Part 2 or client-restricted — removed entirely by X2</t>
         </is>
       </c>
       <c r="F18" s="23" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="G18" s="24">
         <f>ROUND(F18*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>Complex-led</t>
+      <c r="H18" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
         <is>
-          <t>C2 High dollar value</t>
+          <t>Basic-led</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>PCS body-part and device characters, number of sites treated, graft harvesting as a separate procedure, PDx sequencing</t>
-        </is>
-      </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>Highest reimbursement per chart in the pool. Counting treated sites and graft harvest is where the PCS code goes wrong.</t>
+          <t>C8 Foundation</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>Substance use versus abuse versus dependence, withdrawal with complication, psychiatric PDx selection</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>Sourcing is narrow by design: X2 removes most candidates. If eligible supply is not there, report it as a constrained topic rather than forcing the target.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="33" customHeight="1">
       <c r="A19" s="21" t="inlineStr">
         <is>
-          <t>IPD-13</t>
+          <t>IPD-14</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>Surgical DRGs</t>
+          <t>Medical DRGs</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>Digestive surgical — bowel resection, cholecystectomy, hernia repair</t>
+          <t>Other infectious disease</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>Inpatient abdominal surgery, including laparoscopic-to-open conversion and anastomosis as a separate root operation.</t>
+          <t>Infectious admissions that are not sepsis: cellulitis, osteomyelitis, C. difficile, endocarditis, and device-related infection.</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Same-day general surgery — SDS-13</t>
+          <t>Sepsis and septic shock — IPD-08</t>
         </is>
       </c>
       <c r="F19" s="23" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G19" s="24">
         <f>ROUND(F19*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
-        <is>
-          <t>Root operation selection (Excision versus Resection), approach character, conversion coding, post-operative complication with POA</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>Excision versus Resection on a partial organ is the classic PCS error and is worth planting in both directions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>IPD-14</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>Organism specificity, device-related infection coding, PDx sequencing against the device complication, CC/MCC</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>Device-related infection carries a complication code that must be sequenced with the infection; a frequent miss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>SURGICAL DRGS  —  HC Coverage Matrix parent: 45%</t>
+        </is>
+      </c>
+      <c r="F20" s="20">
+        <f>IF(ROUND(SUMIF($B$5:$B$31,"Surgical DRGs",$F$5:$F$31),6)=0.45,"OK — topics sum to the 45% parent","CHECK — topics do not sum to the 45% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="33" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>IPD-15</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>Surgical DRGs</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>Nervous system surgical — craniotomy, shunt, spine decompression</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>Cranial and spinal surgery including shunt revision, which is a different root operation from shunt insertion.</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="n">
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Caesarean delivery</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>Caesarean delivery admissions, which group surgical, including the indication that drives the principal diagnosis and sterilisation performed at the same time.</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Vaginal delivery — IPD-01; the newborn record — IPD-02</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="n">
         <v>0.04</v>
-      </c>
-      <c r="G20" s="24">
-        <f>ROUND(F20*$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
-        <is>
-          <t>Complex-led</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>C2 High dollar value</t>
-        </is>
-      </c>
-      <c r="J20" s="22" t="inlineStr">
-        <is>
-          <t>PCS root operation on a device (Revision, Replacement, Removal), body-part character, laterality, POA</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>Device-related root operations are the least familiar part of PCS and are most often coded as Insertion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>IPD-15</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>Surgical DRGs</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>Genitourinary surgical</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>Nephrectomy, prostatectomy, dialysis access creation and urological procedures requiring admission.</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Cystoscopy and stone procedures done same-day — SDS-16</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="n">
-        <v>0.03</v>
       </c>
       <c r="G21" s="24">
         <f>ROUND(F21*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H21" s="22" t="inlineStr">
-        <is>
-          <t>Moderate-led</t>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>P1 — build first</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
         <is>
-          <t>C8 Foundation</t>
+          <t>Complex-led</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
         <is>
-          <t>PCS body-part laterality, approach character, CC/MCC capture</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr"/>
+          <t>C1 High error rate</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>Principal diagnosis (the indication, not the caesarean), PCS delivery root operation and approach, concurrent sterilisation, Z3A, CC/MCC</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>The caesarean half of the OB priority block. Coding the caesarean itself as the PDx instead of the indication is the error this topic exists to train.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="33" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
@@ -3884,44 +3998,49 @@
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>Respiratory surgical — thoracotomy, tracheostomy, lung resection</t>
+          <t>Obstetric and postpartum surgical procedures</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>Thoracic surgery and tracheostomy, including tracheostomy performed during a long ventilator stay, which changes the DRG entirely.</t>
+          <t>Postpartum haemorrhage requiring intervention, retained products with D&amp;C, obstetric laceration repair, and hysterectomy for an obstetric cause.</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Antepartum and postpartum medical admissions — IPD-04</t>
         </is>
       </c>
       <c r="F22" s="23" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G22" s="24">
         <f>ROUND(F22*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>P1 — build first</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
-        <is>
-          <t>C5 DRGV trending PCS / DRG</t>
-        </is>
-      </c>
       <c r="J22" s="22" t="inlineStr">
         <is>
-          <t>PCS root operation and approach, tracheostomy with ventilator hours, lobe-level body part, POA</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>A tracheostomy on a ventilated patient moves the case to the highest-weight DRG family; missing it is a large-dollar error.</t>
+          <t>C6 Customer escalations</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>PCS root operation for evacuation and repair, postpartum period rules, PDx sequencing, blood product capture</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>Low volume, high error rate. Completes the OB priority block on the surgical side.</t>
         </is>
       </c>
     </row>
@@ -3938,44 +4057,49 @@
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>Obstetric delivery — vaginal and caesarean</t>
+          <t>Digestive surgical — bowel resection, cholecystectomy, hernia repair</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>Delivery admissions, outcome of delivery, and complications of labour. Maternal record only.</t>
+          <t>Inpatient abdominal surgery, including laparoscopic-to-open conversion and anastomosis as a separate root operation.</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Newborn record — IPD-10</t>
+          <t>Same-day general surgery — SDS-12</t>
         </is>
       </c>
       <c r="F23" s="23" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="G23" s="24">
         <f>ROUND(F23*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>C6 Customer escalations</t>
-        </is>
-      </c>
       <c r="J23" s="22" t="inlineStr">
         <is>
-          <t>Principal diagnosis for a delivery admission, Z3A gestational weeks, outcome-of-delivery code, PCS delivery root operation</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>Linked to the newborn record; R3 applies to both. The PDx for a delivery admission is the complication, not the delivery.</t>
+          <t>C8 Foundation</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>Root operation selection (Excision versus Resection), approach character, conversion coding, post-operative complication with POA</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>Excision versus Resection on a partial organ is the classic PCS error and is worth planting in both directions.</t>
         </is>
       </c>
     </row>
@@ -3992,44 +4116,49 @@
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>Vascular access and device procedures — PICC, pacemaker, dialysis catheter</t>
+          <t>Cardiovascular surgical — CABG, valve, PCI, EP procedures</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>Procedures whose DRG is driven by the device rather than the diagnosis, performed during a medical admission.</t>
+          <t>Open and percutaneous cardiac procedures, including multi-vessel PCI with differing stent counts and intraoperative conversion.</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Diagnostic catheterisation with no intervention — out of scope this cycle</t>
         </is>
       </c>
       <c r="F24" s="23" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="G24" s="24">
         <f>ROUND(F24*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H24" s="22" t="inlineStr">
-        <is>
-          <t>Moderate-led</t>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
         <is>
-          <t>C6 Customer escalations</t>
+          <t>Complex-led</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
         <is>
-          <t>PCS device and qualifier characters, central versus peripheral body part, Insertion versus Revision</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>PICC lines are a named customer escalation area in the HC trainer-role sheet. Keep this topic filled.</t>
+          <t>C2 High dollar value</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>PCS body-part and device characters, number of sites treated, graft harvesting as a separate procedure, PDx sequencing</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>Highest reimbursement per chart in the pool. Counting treated sites and graft harvest is where the PCS code goes wrong.</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4175,12 @@
       </c>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>Transplant and other high-weight DRGs</t>
+          <t>Respiratory surgical — thoracotomy, tracheostomy, lung resection</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>Solid-organ transplant, ECMO and other very high relative-weight cases.</t>
+          <t>Thoracic surgery and tracheostomy, including tracheostomy performed during a long ventilator stay, which changes the DRG entirely.</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -4060,34 +4189,39 @@
         </is>
       </c>
       <c r="F25" s="23" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G25" s="24">
         <f>ROUND(F25*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>C2 High dollar value</t>
-        </is>
-      </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>PCS transplant qualifier, ECMO coding, PDx sequencing, MCC capture</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>Low volume by nature. One or two charts per refresh is the realistic supply; do not inflate the weight to force a count.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+          <t>C5 DRGV trending PCS / DRG</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>PCS root operation and approach, tracheostomy with ventilator hours, lobe-level body part, POA</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>A tracheostomy on a ventilated patient moves the case to the highest-weight DRG family; missing it is a large-dollar error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="33" customHeight="1">
       <c r="A26" s="21" t="inlineStr">
         <is>
           <t>IPD-20</t>
@@ -4100,79 +4234,375 @@
       </c>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>Multiple significant trauma and burns</t>
+          <t>Musculoskeletal — joint replacement, spinal fusion, fracture fixation</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>Polytrauma and significant burn admissions, where sequencing rules are specific and code volume is high.</t>
+          <t>Elective and traumatic MSK surgery requiring admission. Approach and device-value axes of the PCS code, fusion level counts.</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Single-site injury seen in the ED — EDF-06</t>
+          <t>Same-day orthopaedic procedures — SDS-01 to SDS-03</t>
         </is>
       </c>
       <c r="F26" s="23" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="G26" s="24">
         <f>ROUND(F26*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>Moderate-led</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>C5 DRGV trending PCS / DRG</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>PCS root operation and device character, fusion levels and approach, bilateral procedures, POA on post-operative conditions</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>Highest-volume surgical family and the best place to train PCS character selection. Carries the device-value character the auditor module plants against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="33" customHeight="1">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>IPD-21</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Surgical DRGs</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Nervous system surgical — craniotomy, shunt, spine decompression</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>Cranial and spinal surgery including shunt revision, which is a different root operation from shunt insertion.</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G27" s="24">
+        <f>ROUND(F27*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="J27" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>PCS root operation on a device (Revision, Replacement, Removal), body-part character, laterality, POA</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>Device-related root operations are the least familiar part of PCS and are most often coded as Insertion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>IPD-22</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Surgical DRGs</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Genitourinary surgical</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>Nephrectomy, prostatectomy, dialysis access creation and urological procedures requiring admission.</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Cystoscopy and stone procedures done same-day — SDS-15</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G28" s="24">
+        <f>ROUND(F28*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>Moderate-led</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>C8 Foundation</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>PCS body-part laterality, approach character, CC/MCC capture</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="33" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>IPD-23</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Surgical DRGs</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>Vascular access and device procedures — PICC, pacemaker, dialysis catheter</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>Procedures whose DRG is driven by the device rather than the diagnosis, performed during a medical admission.</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G29" s="24">
+        <f>ROUND(F29*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>Moderate-led</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>C6 Customer escalations</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>PCS device and qualifier characters, central versus peripheral body part, Insertion versus Revision</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>PICC lines are a named customer escalation area in the HC trainer-role sheet. Keep this topic filled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="33" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>IPD-24</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Surgical DRGs</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Transplant and other high-weight DRGs</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>Solid-organ transplant, ECMO and other very high relative-weight cases.</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G30" s="24">
+        <f>ROUND(F30*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>Complex-led</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>C2 High dollar value</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>PCS transplant qualifier, ECMO coding, PDx sequencing, MCC capture</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>Low volume by nature. One or two charts per refresh is the realistic supply; do not inflate the weight to force a count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>IPD-25</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Surgical DRGs</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>Multiple significant trauma and burns</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Polytrauma and significant burn admissions, where sequencing rules are specific and code volume is high.</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Single-site injury seen in the ED — EDF-06</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G31" s="24">
+        <f>ROUND(F31*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>Complex-led</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>C2 High dollar value</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>Multiple significant trauma DRG criteria, burn TBSA coding, injury sequencing, POA</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="L31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F27" s="26">
-        <f>SUM(F5:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="27">
-        <f>SUM(G5:G26)</f>
-        <v/>
-      </c>
-      <c r="H27" s="25" t="inlineStr">
+      <c r="F32" s="29">
+        <f>SUM(F5:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="30">
+        <f>SUM(G5:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="28" t="inlineStr">
         <is>
           <t>Weights must total 100%</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="39" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+    <row r="34" ht="39" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Shaded Topic %% cells are the only editable numbers on this sheet. Target charts recalculates from the pool on Specialty Summary. Edit a weight and the category check in its band row will read CHECK until the other weights in that category are rebalanced — the sheet is built to refuse a topic that quietly grows at its neighbours' expense.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Target charts is a ceiling, not a quota to fill at any cost. Where eligible supply genuinely is not there — a topic narrowed by exclusion X2, or a low-volume case type — report it as constrained in the gap review rather than substituting charts from an adjacent topic.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="14" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Variance in the strip above is rounding drift between the sum of topic targets and the pool. The pool is the authority.</t>
         </is>
@@ -4180,17 +4610,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F16:K16"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="H32:L32"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A36:L36"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="F20:L20"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="A35:L35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4202,7 +4632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4212,10 +4642,11 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4310,22 +4741,28 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
+          <t>Build
+priority</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
           <t>Difficulty
 skew</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Primary sourcing
 channel</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Key elements the chart must exercise</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -4375,22 +4812,27 @@
         <f>ROUND(F6*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>Facility level criteria and the point-based acuity tool, diagnosis specificity, discharge disposition</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>The main source of Week 1 Basic-tier charts for ED. Keep this topic full or Week 1 has nothing to run on.</t>
         </is>
@@ -4429,22 +4871,27 @@
         <f>ROUND(F7*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>Whether a facility level is billable at all, ancillary-only service coding, diagnosis linkage</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="L7" s="11" t="inlineStr">
         <is>
           <t>Teaches the lower bound of the ladder: the correct answer is sometimes that no E/M level applies.</t>
         </is>
@@ -4483,22 +4930,27 @@
         <f>ROUND(F8*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>Procedure versus facility level interaction, separately reportable service, laterality and site</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr"/>
+      <c r="L8" s="11" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -4544,22 +4996,27 @@
         <f>ROUND(F10*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>Facility level criteria, diagnosis specificity, medication administration capture</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr"/>
+      <c r="L10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="21" t="inlineStr">
@@ -4594,22 +5051,27 @@
         <f>ROUND(F11*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>Repair length and complexity tiers, anatomic site grouping, injury external cause, facility level</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="L11" s="11" t="inlineStr">
         <is>
           <t>Summing repair lengths across sites in the same anatomic group is the recurring error here.</t>
         </is>
@@ -4638,7 +5100,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Injuries admitted for operative fixation — IP-DRG (IPD-11)</t>
+          <t>Injuries admitted for operative fixation — IP-DRG (IPD-20)</t>
         </is>
       </c>
       <c r="F12" s="23" t="n">
@@ -4648,22 +5110,27 @@
         <f>ROUND(F12*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>Fracture site and laterality, initial encounter character, splint and strapping application, facility level</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>The seventh character for encounter type is the most frequently wrong element in this topic.</t>
         </is>
@@ -4702,22 +5169,27 @@
         <f>ROUND(F13*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>Infusion hierarchy (chemo, therapeutic, hydration), initial versus sequential versus concurrent, units by time, diagnosis linkage</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>The infusion hierarchy and the start/stop time arithmetic are a denial-trend area; source from the denial report.</t>
         </is>
@@ -4767,22 +5239,27 @@
         <f>ROUND(F15*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>Facility level criteria at the 4/5 boundary, symptom versus confirmed diagnosis, serial diagnostic capture</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>Teaches coding to a symptom when no diagnosis was reached — the correct answer is often the symptom code.</t>
         </is>
@@ -4821,22 +5298,27 @@
         <f>ROUND(F16*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>Exacerbation documentation, nebuliser and ventilation management capture, facility level, diagnosis specificity</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr"/>
+      <c r="L16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="33" customHeight="1">
       <c r="A17" s="21" t="inlineStr">
@@ -4871,22 +5353,27 @@
         <f>ROUND(F17*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>Facility level at the 4/5 boundary, comorbidity capture, diagnosis sequencing, extent of workup</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="L17" s="11" t="inlineStr">
         <is>
           <t>The level 4 versus 5 call is the highest-volume error in ED facility coding; this topic exists to train the boundary.</t>
         </is>
@@ -4925,22 +5412,27 @@
         <f>ROUND(F18*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>C6 Customer escalations</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>Facility level where time and monitoring drive acuity, substance use coding, suicidal ideation coding, disposition</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>Constrained supply under X2. Report as constrained rather than forcing the count.</t>
         </is>
@@ -4979,22 +5471,27 @@
         <f>ROUND(F19*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>Observation hour counting, whether the ED level is separately reportable, status determination, diagnosis supporting observation</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="L19" s="11" t="inlineStr">
         <is>
           <t>Observation hour counting is a denial-trend area and is routinely coded from the order time rather than the clock time.</t>
         </is>
@@ -5044,22 +5541,27 @@
         <f>ROUND(F21*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>Facility level 5 criteria, extent of intervention, diagnosis specificity, comorbidity capture</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr"/>
+      <c r="L21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
@@ -5094,22 +5596,27 @@
         <f>ROUND(F22*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>Critical care qualification, time documentation, bundled versus separately reportable procedures, facility level interaction</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>Whether the condition qualifies as critical care at all is the hardest question in the ED. The time arithmetic is not the training point and is not where coders go wrong.</t>
         </is>
@@ -5148,22 +5655,27 @@
         <f>ROUND(F23*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>Trauma activation criteria and pre-notification requirement, revenue code use, injury coding, facility level</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="L23" s="11" t="inlineStr">
         <is>
           <t>The activation charge requires pre-hospital notification; charts missing it teach the denial.</t>
         </is>
@@ -5202,38 +5714,43 @@
         <f>ROUND(F24*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>Resuscitation procedure coding, critical care interaction, disposition including expired, diagnosis sequencing</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr"/>
+      <c r="L24" s="11" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="29">
         <f>SUM(F5:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="30">
         <f>SUM(G5:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H25" s="28" t="inlineStr">
         <is>
           <t>Weights must total 100%</t>
         </is>
@@ -5262,21 +5779,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="F20:K20"/>
-    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="F14:L14"/>
+    <mergeCell ref="A29:L29"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="F14:K14"/>
+    <mergeCell ref="H25:L25"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="A28:L28"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F9:K9"/>
-    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="F20:L20"/>
     <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="F5:L5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5288,7 +5805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5298,10 +5815,11 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -5396,22 +5914,28 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
+          <t>Build
+priority</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
           <t>Difficulty
 skew</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Primary sourcing
 channel</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Key elements the chart must exercise</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -5461,22 +5985,27 @@
         <f>ROUND(F6*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>MDM-based level selection, problem addressed, diagnosis specificity</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>Graded on the ED ladder in services/em_levels.py, which is separate from the office ladders. Same level on the wrong ladder is a distinct error from a near miss on the right one.</t>
         </is>
@@ -5526,22 +6055,27 @@
         <f>ROUND(F8*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>COPA, Data Review and Risk as three MDM levels, the 2-of-3 rule, diagnosis specificity</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>MDM is audited as three levels, never as element ticks.</t>
         </is>
@@ -5580,22 +6114,27 @@
         <f>ROUND(F9*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>Modifier 25 appropriateness, procedure versus E/M separation, MDM level, laterality</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="L9" s="11" t="inlineStr">
         <is>
           <t>Modifier 25 is the single most audited modifier in ED profee coding.</t>
         </is>
@@ -5645,22 +6184,27 @@
         <f>ROUND(F11*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>COPA, Data Review, Risk, the 2-of-3 rule, prescription drug management as a risk element</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="L11" s="11" t="inlineStr">
         <is>
           <t>The 99284/99285 boundary carries the most level errors; plant in both directions so upcoding and downcoding both appear.</t>
         </is>
@@ -5699,22 +6243,27 @@
         <f>ROUND(F12*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>Global period of the procedure, modifier 25 and 57, procedure code selection, MDM level</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -5760,22 +6309,27 @@
         <f>ROUND(F14*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>COPA at the highest level, data categories, risk including decision for hospitalisation, the 2-of-3 rule</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr"/>
+      <c r="L14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="21" t="inlineStr">
@@ -5810,22 +6364,27 @@
         <f>ROUND(F15*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>C6 Customer escalations</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>Critical care qualification, organ system failure, time documentation, MDM level if not critical care</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>The hardest question in the ED and the one a generated error cannot invent. These charts need AnswerKey.cc_boundary set to borderline before the auditor module will plant against them.</t>
         </is>
@@ -5875,22 +6434,27 @@
         <f>ROUND(F17*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>Critical care qualification, bundled procedures, separately reportable procedures, diagnosis sequencing</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="L17" s="11" t="inlineStr">
         <is>
           <t>The 99292 unit count follows from the time and is not where coders go wrong; critical care time itself is never planted. An auditor validates the code, not the arithmetic.</t>
         </is>
@@ -5940,22 +6504,27 @@
         <f>ROUND(F19*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>Procedure code selection, modifier 25 and 59, bundling against the E/M, laterality and site</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr"/>
+      <c r="L19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="21" t="inlineStr">
@@ -5990,22 +6559,27 @@
         <f>ROUND(F20*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>Which code family applies, same-day E/M rules, modifier 25, diagnosis supporting the status</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr"/>
+      <c r="L20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="33" customHeight="1">
       <c r="A21" s="21" t="inlineStr">
@@ -6040,42 +6614,47 @@
         <f>ROUND(F21*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>C6 Customer escalations</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>Split/shared substantive portion, teaching physician attestation, modifier use, MDM level</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="L21" s="11" t="inlineStr">
         <is>
           <t>A documentation-rule topic rather than a code-selection one: the correct answer sometimes is that the service is not billable as documented.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="29">
         <f>SUM(F5:F21)</f>
         <v/>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="30">
         <f>SUM(G5:G21)</f>
         <v/>
       </c>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>Weights must total 100%</t>
         </is>
@@ -6104,24 +6683,24 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="F18:K18"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="F13:L13"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="F13:K13"/>
-    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="F10:L10"/>
+    <mergeCell ref="F16:L16"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="F7:L7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F10:K10"/>
-    <mergeCell ref="F16:K16"/>
+    <mergeCell ref="H22:L22"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="F18:L18"/>
+    <mergeCell ref="A24:L24"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6134,7 +6713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6144,10 +6723,11 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -6242,22 +6822,28 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
+          <t>Build
+priority</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
           <t>Difficulty
 skew</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Primary sourcing
 channel</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Key elements the chart must exercise</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -6307,22 +6893,27 @@
         <f>ROUND(F6*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>New versus established determination, COPA, Data Review, Risk, the 2-of-3 rule</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>New-patient and established-patient office visits are separate ladders. The same level on the wrong ladder is the new-versus-established error, not a near miss.</t>
         </is>
@@ -6361,22 +6952,27 @@
         <f>ROUND(F7*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>COPA for a stable chronic condition, Data Review, Risk, the 2-of-3 rule</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="L7" s="11" t="inlineStr">
         <is>
           <t>The highest-volume topic in the specialty and the main Week 1 source. 99213 versus 99214 is the most common level error in outpatient coding.</t>
         </is>
@@ -6415,22 +7011,27 @@
         <f>ROUND(F8*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>Initial versus subsequent determination, COPA, Data Review, Risk, admission date rules</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr"/>
+      <c r="L8" s="11" t="inlineStr"/>
     </row>
     <row r="9" ht="33" customHeight="1">
       <c r="A9" s="21" t="inlineStr">
@@ -6465,22 +7066,27 @@
         <f>ROUND(F9*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>Subsequent care ladder, interval history, COPA, Risk</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="L9" s="11" t="inlineStr">
         <is>
           <t>The inpatient ladder is distinct from both office ladders; a chart coded on the wrong ladder is a classifier error, not a level error.</t>
         </is>
@@ -6519,22 +7125,27 @@
         <f>ROUND(F10*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>Age-banded preventive code selection, AWV versus preventive distinction, modifier 25 for a same-day problem visit, diagnosis linkage</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Not graded on medical decision making at all: applicable_weights drops the MDM weights for preventive charts, and sections_for_chart resolves the form per chart. A chart with no key keeps the full form, because absence is not evidence it is preventive.</t>
         </is>
@@ -6584,22 +7195,27 @@
         <f>ROUND(F12*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>COPA for multiple or chronic problems, data categories, prescription drug management as risk, the 2-of-3 rule</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="33" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
@@ -6634,22 +7250,27 @@
         <f>ROUND(F13*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>COPA, Data Review, Risk, the 2-of-3 rule, chronic condition exacerbation documentation</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>Largest single topic in the pool. Plant level errors in both directions here: upcoding is what payers audit for, downcoding is revenue quietly left behind.</t>
         </is>
@@ -6688,22 +7309,27 @@
         <f>ROUND(F14*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>COPA, data categories, risk of morbidity, initial versus subsequent</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr"/>
+      <c r="L14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="33" customHeight="1">
       <c r="A15" s="21" t="inlineStr">
@@ -6738,22 +7364,27 @@
         <f>ROUND(F15*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>Subsequent care ladder, COPA for an inadequately responding problem, Data Review, Risk</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="33" customHeight="1">
       <c r="A16" s="21" t="inlineStr">
@@ -6788,22 +7419,27 @@
         <f>ROUND(F16*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>C6 Customer escalations</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>Consultation requirements (request, reason, report), consult versus transfer of care, COPA, Data Review, Risk</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="L16" s="11" t="inlineStr">
         <is>
           <t>Consults are off-ladder for planting purposes: em_levels.py knows three ladders plus critical care, so a consult is not a near miss along any of them.</t>
         </is>
@@ -6853,22 +7489,27 @@
         <f>ROUND(F18*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>COPA at the highest level, independent interpretation and external discussion as data, high risk</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr"/>
+      <c r="L18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="21" t="inlineStr">
@@ -6903,22 +7544,27 @@
         <f>ROUND(F19*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>COPA for severe exacerbation, data categories, high risk including drug therapy requiring monitoring</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr"/>
+      <c r="L19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="21" t="inlineStr">
@@ -6953,22 +7599,27 @@
         <f>ROUND(F20*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>COPA, data categories, risk including decision for escalation of care</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr"/>
+      <c r="L20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="21" t="inlineStr">
@@ -7003,22 +7654,27 @@
         <f>ROUND(F21*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>COPA for an unstable problem, Data Review, Risk</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr"/>
+      <c r="L21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
@@ -7053,22 +7709,27 @@
         <f>ROUND(F22*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>C6 Customer escalations</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>Consultation requirements, COPA, data categories, high risk</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>Off-ladder; see EM-10.</t>
         </is>
@@ -7107,22 +7768,27 @@
         <f>ROUND(F23*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>Time thresholds, what counts toward total time on the date of service, add-on code units, same-day rules</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="L23" s="11" t="inlineStr">
         <is>
           <t>Time-based rather than MDM-based, so MDM weights do not apply. These are the charts behind the HC Method split of 80% MDM / 20% time.</t>
         </is>
@@ -7161,42 +7827,47 @@
         <f>ROUND(F24*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>C6 Customer escalations</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>Substantive portion determination, modifier and place-of-service selection, telehealth modifier use, MDM or time level</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="L24" s="11" t="inlineStr">
         <is>
           <t>Named in the HC coverage matrix as a must-include for this specialty.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="29">
         <f>SUM(F5:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="30">
         <f>SUM(G5:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H25" s="28" t="inlineStr">
         <is>
           <t>Weights must total 100%</t>
         </is>
@@ -7225,19 +7896,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="F11:K11"/>
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="H25:L25"/>
+    <mergeCell ref="F17:L17"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="I2:L2"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="F17:K17"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="F5:L5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7249,7 +7920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7259,10 +7930,11 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -7357,22 +8029,28 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
+          <t>Build
+priority</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
           <t>Difficulty
 skew</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Primary sourcing
 channel</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Key elements the chart must exercise</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -7412,7 +8090,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Arthroplasty requiring admission — IP-DRG (IPD-11)</t>
+          <t>Arthroplasty requiring admission — IP-DRG (IPD-20)</t>
         </is>
       </c>
       <c r="F6" s="23" t="n">
@@ -7422,22 +8100,27 @@
         <f>ROUND(F6*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>Multiple procedure bundling in one compartment, modifier 51 and 59, laterality, implant and device capture</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>Separately reportable versus bundled within the same compartment is the recurring error.</t>
         </is>
@@ -7476,22 +8159,27 @@
         <f>ROUND(F7*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>Digit-specific modifiers, number of structures treated, laterality, bundling</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
@@ -7526,22 +8214,27 @@
         <f>ROUND(F8*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>Reduction versus manipulation, global period, hardware removal coding, laterality</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr"/>
+      <c r="L8" s="11" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -7587,22 +8280,27 @@
         <f>ROUND(F10*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>Screening versus diagnostic determination, modifier 33 and PT, diagnosis sequencing, patient liability consequence</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>A screening that converts to diagnostic changes both the code and the patient's liability. The highest-frequency denial topic in SDS.</t>
         </is>
@@ -7641,22 +8339,27 @@
         <f>ROUND(F11*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>Technique-specific code selection, one code per technique rule, modifier 59, diagnosis linkage</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="L11" s="11" t="inlineStr">
         <is>
           <t>Coders routinely report one code per polyp rather than one per technique; a clean error to plant.</t>
         </is>
@@ -7695,22 +8398,27 @@
         <f>ROUND(F12*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>Multiple endoscopy rules, modifier 51, base code selection, diagnosis linkage</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -7756,22 +8464,27 @@
         <f>ROUND(F14*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>Complex versus routine criteria, laterality, staged bilateral procedures, device capture</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>High volume and largely formulaic, which makes it a reliable Basic-tier source.</t>
         </is>
@@ -7810,22 +8523,27 @@
         <f>ROUND(F15*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>Bilateral and laterality modifiers, repeat service within a period, drug units, diagnosis linkage</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="21" t="inlineStr">
@@ -7860,22 +8578,27 @@
         <f>ROUND(F16*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>Functional versus cosmetic documentation, laterality, bundling, diagnosis supporting medical necessity</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr"/>
+      <c r="L16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -7921,22 +8644,27 @@
         <f>ROUND(F18*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>Level counting and add-on codes, bilateral reporting, imaging guidance bundling, MUE limits</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>Level counting against the MUE limit is the specific failure; the units are where it goes wrong, not the base code.</t>
         </is>
@@ -7975,22 +8703,27 @@
         <f>ROUND(F19*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>Nerve-specific code selection, level and laterality units, prior diagnostic block requirement, imaging bundling</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr"/>
+      <c r="L19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -8026,7 +8759,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Cases requiring admission — IP-DRG (IPD-13)</t>
+          <t>Cases requiring admission — IP-DRG (IPD-17)</t>
         </is>
       </c>
       <c r="F21" s="23" t="n">
@@ -8036,22 +8769,27 @@
         <f>ROUND(F21*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>Hernia type, approach and reducibility, lesion size including margins, approach character, bundling</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr"/>
+      <c r="L21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
@@ -8076,7 +8814,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Delivery admissions — IP-DRG (IPD-17)</t>
+          <t>Delivery admissions — IP-DRG (IPD-01 / IPD-15)</t>
         </is>
       </c>
       <c r="F22" s="23" t="n">
@@ -8086,22 +8824,27 @@
         <f>ROUND(F22*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>Diagnostic versus operative, bundling within one approach, modifier 59, diagnosis linkage</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr"/>
+      <c r="L22" s="11" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="21" t="inlineStr">
@@ -8136,22 +8879,27 @@
         <f>ROUND(F23*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>Bilateral and multiple-site reporting, age-banded code selection, bundling</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr"/>
+      <c r="L23" s="11" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="21" t="inlineStr">
@@ -8176,7 +8924,7 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Procedures requiring admission — IP-DRG (IPD-15)</t>
+          <t>Procedures requiring admission — IP-DRG (IPD-22)</t>
         </is>
       </c>
       <c r="F24" s="23" t="n">
@@ -8186,38 +8934,43 @@
         <f>ROUND(F24*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>Base versus more extensive procedure, bundling of the cystoscopy, laterality, stent placement</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr"/>
+      <c r="L24" s="11" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="29">
         <f>SUM(F5:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="30">
         <f>SUM(G5:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H25" s="28" t="inlineStr">
         <is>
           <t>Weights must total 100%</t>
         </is>
@@ -8246,23 +8999,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="F20:K20"/>
-    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="H25:L25"/>
+    <mergeCell ref="F13:L13"/>
+    <mergeCell ref="F17:L17"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="F20:L20"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="F13:K13"/>
-    <mergeCell ref="F17:K17"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F9:K9"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="F5:L5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8274,7 +9027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8284,10 +9037,11 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -8382,22 +9136,28 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
+          <t>Build
+priority</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
           <t>Difficulty
 skew</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Primary sourcing
 channel</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Key elements the chart must exercise</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -8447,22 +9207,27 @@
         <f>ROUND(F6*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>Approach and conversion coding, multiple procedure bundling, modifier 51 and 59, global period</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>Conversion from laparoscopic to open is coded to the completed approach, not both; a clean error to plant.</t>
         </is>
@@ -8501,22 +9266,27 @@
         <f>ROUND(F7*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>Primary versus revision, component-level coding, level counting and add-ons, laterality, modifier 62 co-surgeon</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="33" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
@@ -8551,22 +9321,27 @@
         <f>ROUND(F8*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>Number of grafts and vessels, harvest as a separate procedure, modifier 62 and 80, bundling of access</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>Highest reimbursement per chart. Counting vessels and reporting harvest separately are the two recurring errors.</t>
         </is>
@@ -8605,22 +9380,27 @@
         <f>ROUND(F9*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>Level counting across decompression and fusion, approach-specific codes, add-on hierarchy, co-surgeon modifiers</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr"/>
+      <c r="L9" s="11" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="21" t="inlineStr">
@@ -8655,22 +9435,27 @@
         <f>ROUND(F10*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>Approach and specimen weight, bundled oophorectomy, global obstetric package, modifier 22</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr"/>
+      <c r="L10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8716,22 +9501,27 @@
         <f>ROUND(F12*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>Approach, bundling of the endoscopic base, laterality, robotic assistance reporting</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
@@ -8766,22 +9556,27 @@
         <f>ROUND(F13*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>Bilateral and multiple-site reporting, neck dissection extent, bundling, modifier 59</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr"/>
+      <c r="L13" s="11" t="inlineStr"/>
     </row>
     <row r="14" ht="33" customHeight="1">
       <c r="A14" s="21" t="inlineStr">
@@ -8816,22 +9611,27 @@
         <f>ROUND(F14*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>Defect size and site, donor site closure, functional versus cosmetic documentation, staged procedure modifiers</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr"/>
+      <c r="L14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="21" t="inlineStr">
@@ -8866,22 +9666,27 @@
         <f>ROUND(F15*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>Laterality and staged bilateral work, bundling, global period, device capture</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="21" t="inlineStr">
@@ -8916,22 +9721,27 @@
         <f>ROUND(F16*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>Modifier 62, 66 and 80, donor versus recipient coding, staged procedure reporting</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr"/>
+      <c r="L16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="33" customHeight="1">
       <c r="A17" s="21" t="inlineStr">
@@ -8966,42 +9776,47 @@
         <f>ROUND(F17*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>Modifiers 58, 76, 77, 78 and 79, global period boundaries, related versus unrelated determination</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="L17" s="11" t="inlineStr">
         <is>
           <t>A modifier-selection topic rather than a code-selection one. Which of 58, 78 and 79 applies is the whole question, and getting it wrong changes payment entirely.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="29">
         <f>SUM(F5:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="30">
         <f>SUM(G5:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="25" t="inlineStr">
+      <c r="H18" s="28" t="inlineStr">
         <is>
           <t>Weights must total 100%</t>
         </is>
@@ -9030,17 +9845,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="F11:K11"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A11:E11"/>
+    <mergeCell ref="H18:L18"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="A21:L21"/>
     <mergeCell ref="A18:E18"/>
+    <mergeCell ref="F5:L5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9052,7 +9867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9062,10 +9877,11 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -9160,22 +9976,28 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
+          <t>Build
+priority</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
           <t>Difficulty
 skew</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Primary sourcing
 channel</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Key elements the chart must exercise</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -9225,22 +10047,27 @@
         <f>ROUND(F6*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>Facility acuity tool and professional MDM applied to one record, diagnosis specificity, disposition</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>Mirrors EDF-01 and EDP-01, but the charts are not shared between pools: a single-path chart is graded on both components at once and belongs only here.</t>
         </is>
@@ -9290,22 +10117,27 @@
         <f>ROUND(F8*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>Basic-led</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>C8 Foundation</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>Facility level criteria, professional MDM (COPA, Data, Risk), diagnosis specificity</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>Mirrors EDF-04 and EDP-02.</t>
         </is>
@@ -9355,22 +10187,27 @@
         <f>ROUND(F10*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>Facility level at the 4/5 boundary, professional MDM and the 2-of-3 rule, comorbidity capture</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Mirrors EDF-08 to EDF-10 and EDP-04.</t>
         </is>
@@ -9420,22 +10257,27 @@
         <f>ROUND(F12*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>Facility level 5 criteria, professional COPA, data and risk at the highest level, diagnosis sequencing</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>Mirrors EDF-13 and EDP-06. The largest topic in this pool, as it is on both parent ladders.</t>
         </is>
@@ -9485,22 +10327,27 @@
         <f>ROUND(F14*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>Critical care qualification, bundled versus separately reportable procedures, facility level interaction, diagnosis sequencing</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>Whether the condition qualified as critical care at all is the training point. The 99292 unit count follows from the time and is not planted.</t>
         </is>
@@ -9550,22 +10397,27 @@
         <f>ROUND(F16*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>Moderate-led</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>C1 High error rate</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>Procedure code selection, modifier 25 and 59 on the professional side, facility charge capture, bundling</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr"/>
+      <c r="L16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="21" t="inlineStr">
@@ -9600,22 +10452,27 @@
         <f>ROUND(F17*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>C7 Denial trends</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>Observation hour counting on the facility side, which professional code family applies, status determination</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr"/>
+      <c r="L17" s="11" t="inlineStr"/>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
@@ -9650,42 +10507,47 @@
         <f>ROUND(F18*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
+        <is>
+          <t>P3 — build last</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>C6 Customer escalations</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>Both level determinations on one record, why they diverge, documentation supporting each</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>The reason single path is its own specialty rather than a view of the other two. A coder who assumes the two levels must match is the error this topic exists to find.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="29">
         <f>SUM(F5:F18)</f>
         <v/>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="30">
         <f>SUM(G5:G18)</f>
         <v/>
       </c>
-      <c r="H19" s="25" t="inlineStr">
+      <c r="H19" s="28" t="inlineStr">
         <is>
           <t>Weights must total 100%</t>
         </is>
@@ -9714,25 +10576,25 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="F5:K5"/>
+    <mergeCell ref="F13:L13"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="F9:L9"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="A21:L21"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="F13:K13"/>
-    <mergeCell ref="F9:K9"/>
-    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="F7:L7"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="F11:K11"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F15:L15"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="F7:K7"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="F15:K15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/PracticeLab_Chart_Composition_Taxonomy.xlsx
+++ b/docs/PracticeLab_Chart_Composition_Taxonomy.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
+    <row r="21" ht="65" customHeight="1">
       <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Build priority</t>
@@ -802,7 +802,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>P1, P2 or P3 per topic, in a column of its own, because priority and volume are different questions. The weight says how many charts a topic should hold once the pool is complete; the priority says which topics are sourced and built before it is. IP-DRG leads with the OB and newborn block across both medical and surgical DRGs, then GI, respiratory and cardiovascular.</t>
+          <t>P1 (build first) to P4 (build last) per topic, in a column of its own, because priority and volume are different questions. The weight says how many charts a topic should hold once the pool is complete; the priority says which topics are sourced and built before it is. IP-DRG leads with the OB and newborn block across both medical and surgical DRGs, then GI, respiratory and cardiovascular. E/M leads with level 3 and 4 office visits and the inpatient and observation trio.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
+    <row r="16" ht="33" customHeight="1">
       <c r="A16" s="21" t="inlineStr">
         <is>
           <t>E/M</t>
@@ -1204,23 +1204,23 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Service family</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>Low (levels 2–3)</t>
+          <t>Office / outpatient visits</t>
         </is>
       </c>
       <c r="D16" s="31" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="E16" s="32" t="n">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Carried from HC Chart Selection section 6</t>
+          <t>Not in the HC model — set 2026-10-15 with this workbook. REPLACES the HC Level split as this specialty's parent dimension — see note below.</t>
         </is>
       </c>
     </row>
@@ -1229,18 +1229,18 @@
       <c r="B17" s="22" t="inlineStr"/>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>Moderate (level 4)</t>
+          <t>Time-based and prolonged services</t>
         </is>
       </c>
       <c r="D17" s="31" t="n">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="E17" s="32" t="n">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Carried from HC Chart Selection section 6</t>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
         </is>
       </c>
     </row>
@@ -1249,42 +1249,38 @@
       <c r="B18" s="22" t="inlineStr"/>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>High (level 5)</t>
+          <t>Preventive and wellness</t>
         </is>
       </c>
       <c r="D18" s="31" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="E18" s="32" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Carried from HC Chart Selection section 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="55" customHeight="1">
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
       <c r="A19" s="22" t="inlineStr"/>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
+      <c r="B19" s="22" t="inlineStr"/>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>MDM-based</t>
+          <t>Office procedures with an E/M</t>
         </is>
       </c>
       <c r="D19" s="31" t="n">
-        <v>0.8</v>
+        <v>0.05</v>
       </c>
       <c r="E19" s="32" t="n">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Carried from HC Chart Selection section 6. Cross-cutting. Preventive visits, consults and time-levelled visits are not graded on medical decision making at all, so applicable_weights drops the MDM weights for them and the form is resolved per chart.</t>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
         </is>
       </c>
     </row>
@@ -1293,66 +1289,58 @@
       <c r="B20" s="22" t="inlineStr"/>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>Time-based</t>
+          <t>Care management and transitional care</t>
         </is>
       </c>
       <c r="D20" s="31" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Carried from HC Chart Selection section 6. Topics EM-05, EM-16 and EM-17 are where these charts come from.</t>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="33" t="inlineStr"/>
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Must include</t>
-        </is>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>New versus established · office versus hospital · modifier 25 · split and shared visits</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="n"/>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="35" t="inlineStr">
-        <is>
-          <t>Carried from HC Chart Selection section 6</t>
+      <c r="A21" s="22" t="inlineStr"/>
+      <c r="B21" s="22" t="inlineStr"/>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Telehealth</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E21" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>SDS</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>Service line</t>
-        </is>
-      </c>
+      <c r="A22" s="22" t="inlineStr"/>
+      <c r="B22" s="22" t="inlineStr"/>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>Orthopaedics</t>
+          <t>Inpatient and observation</t>
         </is>
       </c>
       <c r="D22" s="31" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>Carried from HC Chart Selection section 6</t>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
         </is>
       </c>
     </row>
@@ -1361,18 +1349,18 @@
       <c r="B23" s="22" t="inlineStr"/>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>GI / endoscopy</t>
+          <t>Critical care and neonatal intensive care</t>
         </is>
       </c>
       <c r="D23" s="31" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="E23" s="32" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Carried from HC Chart Selection section 6</t>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
         </is>
       </c>
     </row>
@@ -1381,38 +1369,42 @@
       <c r="B24" s="22" t="inlineStr"/>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>Consultations</t>
         </is>
       </c>
       <c r="D24" s="31" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="E24" s="32" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>Carried from HC Chart Selection section 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
       <c r="A25" s="22" t="inlineStr"/>
-      <c r="B25" s="22" t="inlineStr"/>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Level (cross-cutting)</t>
+        </is>
+      </c>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>Pain management</t>
+          <t>Low (levels 2–3)</t>
         </is>
       </c>
       <c r="D25" s="31" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="E25" s="32" t="n">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Carried from HC Chart Selection section 6</t>
+          <t>Carried from HC Chart Selection section 6. Now checked ACROSS the pool rather than decomposed, because AWV, TCM, CCM, telehealth and NICU per-diem codes are not levels at all.</t>
         </is>
       </c>
     </row>
@@ -1421,14 +1413,14 @@
       <c r="B26" s="22" t="inlineStr"/>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>Other surgical</t>
+          <t>Moderate (level 4)</t>
         </is>
       </c>
       <c r="D26" s="31" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E26" s="32" t="n">
-        <v>26</v>
+        <v>165</v>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
@@ -1436,111 +1428,115 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="33" t="inlineStr"/>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>Must include</t>
-        </is>
-      </c>
-      <c r="C27" s="33" t="inlineStr">
-        <is>
-          <t>Modifiers (bilateral, distinct procedure) · implants and devices</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="n"/>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="35" t="inlineStr">
-        <is>
-          <t>Carried from HC Chart Selection section 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>ED Profee</t>
-        </is>
-      </c>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="22" t="inlineStr"/>
+      <c r="B27" s="22" t="inlineStr"/>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>High (level 5)</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E27" s="32" t="n">
+        <v>103</v>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Carried from HC Chart Selection section 6. Runs 10-15% of production; the pool holds 7% deliberately, since a training pool weights the hard calls rather than mirroring the mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="55" customHeight="1">
+      <c r="A28" s="22" t="inlineStr"/>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>ED E/M level</t>
+          <t>Method (cross-cutting)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
         <is>
-          <t>Low acuity (99281 / 99282)</t>
+          <t>MDM-based</t>
         </is>
       </c>
       <c r="D28" s="31" t="n">
-        <v>0.08</v>
+        <v>0.8</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>32</v>
+        <v>330</v>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
+          <t>Carried from HC Chart Selection section 6. Preventive visits, consults, per-diem neonatal care and time-levelled visits are not graded on medical decision making at all, so applicable_weights drops the MDM weights and the form is resolved per chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="33" customHeight="1">
       <c r="A29" s="22" t="inlineStr"/>
       <c r="B29" s="22" t="inlineStr"/>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>Moderate (99283)</t>
+          <t>Time-based</t>
         </is>
       </c>
       <c r="D29" s="31" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
+          <t>Carried from HC Chart Selection section 6. Topics EM-07, EM-14, EM-18 and EM-21 are where these charts come from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="33" customHeight="1">
+      <c r="A30" s="33" t="inlineStr"/>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>Must include</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>New versus established · office versus hospital · modifier 25 · AWV initial versus subsequent · telehealth place of service</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
           <t>Not in the HC model — set 2026-10-15 with this workbook</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="22" t="inlineStr"/>
-      <c r="B30" s="22" t="inlineStr"/>
-      <c r="C30" s="22" t="inlineStr">
-        <is>
-          <t>Level 4 (99284)</t>
-        </is>
-      </c>
-      <c r="D30" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E30" s="32" t="n">
-        <v>80</v>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
-        </is>
-      </c>
-    </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="22" t="inlineStr"/>
-      <c r="B31" s="22" t="inlineStr"/>
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>SDS</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Service line</t>
+        </is>
+      </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>Level 5 (99285)</t>
+          <t>Orthopaedics</t>
         </is>
       </c>
       <c r="D31" s="31" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="E31" s="32" t="n">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+          <t>Carried from HC Chart Selection section 6</t>
         </is>
       </c>
     </row>
@@ -1549,18 +1545,18 @@
       <c r="B32" s="22" t="inlineStr"/>
       <c r="C32" s="22" t="inlineStr">
         <is>
-          <t>Critical care (99291 / 99292)</t>
+          <t>GI / endoscopy</t>
         </is>
       </c>
       <c r="D32" s="31" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="E32" s="32" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+          <t>Carried from HC Chart Selection section 6</t>
         </is>
       </c>
     </row>
@@ -1569,130 +1565,122 @@
       <c r="B33" s="22" t="inlineStr"/>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>Cross-cutting (procedures, observation, split/shared)</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="D33" s="31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E33" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Carried from HC Chart Selection section 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="22" t="inlineStr"/>
+      <c r="B34" s="22" t="inlineStr"/>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Pain management</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E34" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Carried from HC Chart Selection section 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="22" t="inlineStr"/>
+      <c r="B35" s="22" t="inlineStr"/>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>Other surgical</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E35" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Carried from HC Chart Selection section 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="33" t="inlineStr"/>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>Must include</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>Modifiers (bilateral, distinct procedure) · implants and devices</t>
+        </is>
+      </c>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="35" t="inlineStr">
+        <is>
+          <t>Carried from HC Chart Selection section 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>ED Profee</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>ED E/M level</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>Low acuity (99281 / 99282)</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E37" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="22" t="inlineStr"/>
+      <c r="B38" s="22" t="inlineStr"/>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Moderate (99283)</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="n">
         <v>0.18</v>
       </c>
-      <c r="E33" s="32" t="n">
+      <c r="E38" s="32" t="n">
         <v>72</v>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="33" customHeight="1">
-      <c r="A34" s="33" t="inlineStr"/>
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>Must include</t>
-        </is>
-      </c>
-      <c r="C34" s="33" t="inlineStr">
-        <is>
-          <t>Modifier 25 · the 99285 versus 99291 boundary · split and shared documentation</t>
-        </is>
-      </c>
-      <c r="D34" s="33" t="n"/>
-      <c r="E34" s="34" t="n"/>
-      <c r="F34" s="35" t="inlineStr">
-        <is>
-          <t>Not in the HC model — set 2026-10-15 with this workbook. The boundary charts only plant if AnswerKey.cc_boundary is set to borderline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="21" t="inlineStr">
-        <is>
-          <t>Surgery</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>Service line</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="inlineStr">
-        <is>
-          <t>High-volume service lines (general, ortho, CT/vascular, neuro, gynae)</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E35" s="32" t="n">
-        <v>192</v>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="22" t="inlineStr"/>
-      <c r="B36" s="22" t="inlineStr"/>
-      <c r="C36" s="22" t="inlineStr">
-        <is>
-          <t>Specialty and cross-cutting</t>
-        </is>
-      </c>
-      <c r="D36" s="31" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E36" s="32" t="n">
-        <v>108</v>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="33" t="inlineStr"/>
-      <c r="B37" s="33" t="inlineStr">
-        <is>
-          <t>Must include</t>
-        </is>
-      </c>
-      <c r="C37" s="33" t="inlineStr">
-        <is>
-          <t>Global period and staged procedure modifiers · co-surgeon and assistant modifiers · laterality</t>
-        </is>
-      </c>
-      <c r="D37" s="33" t="n"/>
-      <c r="E37" s="34" t="n"/>
-      <c r="F37" s="35" t="inlineStr">
-        <is>
-          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>ED Single Path</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="inlineStr">
-        <is>
-          <t>Acuity ladder</t>
-        </is>
-      </c>
-      <c r="C38" s="22" t="inlineStr">
-        <is>
-          <t>Low acuity</t>
-        </is>
-      </c>
-      <c r="D38" s="31" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E38" s="32" t="n">
-        <v>24</v>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
@@ -1705,14 +1693,14 @@
       <c r="B39" s="22" t="inlineStr"/>
       <c r="C39" s="22" t="inlineStr">
         <is>
-          <t>Moderate (level 3)</t>
+          <t>Level 4 (99284)</t>
         </is>
       </c>
       <c r="D39" s="31" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="E39" s="32" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
@@ -1725,14 +1713,14 @@
       <c r="B40" s="22" t="inlineStr"/>
       <c r="C40" s="22" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 5 (99285)</t>
         </is>
       </c>
       <c r="D40" s="31" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E40" s="32" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
@@ -1745,14 +1733,14 @@
       <c r="B41" s="22" t="inlineStr"/>
       <c r="C41" s="22" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Critical care (99291 / 99292)</t>
         </is>
       </c>
       <c r="D41" s="31" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="E41" s="32" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
@@ -1765,89 +1753,293 @@
       <c r="B42" s="22" t="inlineStr"/>
       <c r="C42" s="22" t="inlineStr">
         <is>
+          <t>Cross-cutting (procedures, observation, split/shared)</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E42" s="32" t="n">
+        <v>72</v>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="33" customHeight="1">
+      <c r="A43" s="33" t="inlineStr"/>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>Must include</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>Modifier 25 · the 99285 versus 99291 boundary · split and shared documentation</t>
+        </is>
+      </c>
+      <c r="D43" s="33" t="n"/>
+      <c r="E43" s="34" t="n"/>
+      <c r="F43" s="35" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook. The boundary charts only plant if AnswerKey.cc_boundary is set to borderline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>Surgery</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Service line</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>High-volume service lines (general, ortho, CT/vascular, neuro, gynae)</t>
+        </is>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E44" s="32" t="n">
+        <v>192</v>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="22" t="inlineStr"/>
+      <c r="B45" s="22" t="inlineStr"/>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>Specialty and cross-cutting</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E45" s="32" t="n">
+        <v>108</v>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="33" t="inlineStr"/>
+      <c r="B46" s="33" t="inlineStr">
+        <is>
+          <t>Must include</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="inlineStr">
+        <is>
+          <t>Global period and staged procedure modifiers · co-surgeon and assistant modifiers · laterality</t>
+        </is>
+      </c>
+      <c r="D46" s="33" t="n"/>
+      <c r="E46" s="34" t="n"/>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>ED Single Path</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>Acuity ladder</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>Low acuity</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E47" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="22" t="inlineStr"/>
+      <c r="B48" s="22" t="inlineStr"/>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>Moderate (level 3)</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E48" s="32" t="n">
+        <v>54</v>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="22" t="inlineStr"/>
+      <c r="B49" s="22" t="inlineStr"/>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
+      <c r="D49" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E49" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="22" t="inlineStr"/>
+      <c r="B50" s="22" t="inlineStr"/>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E50" s="32" t="n">
+        <v>66</v>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>Not in the HC model — set 2026-10-15 with this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="22" t="inlineStr"/>
+      <c r="B51" s="22" t="inlineStr"/>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
           <t>Critical care</t>
         </is>
       </c>
-      <c r="D42" s="31" t="n">
+      <c r="D51" s="31" t="n">
         <v>0.12</v>
       </c>
-      <c r="E42" s="32" t="n">
+      <c r="E51" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Not in the HC model — set 2026-10-15 with this workbook</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="22" t="inlineStr"/>
-      <c r="B43" s="22" t="inlineStr"/>
-      <c r="C43" s="22" t="inlineStr">
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="22" t="inlineStr"/>
+      <c r="B52" s="22" t="inlineStr"/>
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>Cross-cutting</t>
         </is>
       </c>
-      <c r="D43" s="31" t="n">
+      <c r="D52" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E43" s="32" t="n">
+      <c r="E52" s="32" t="n">
         <v>60</v>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Not in the HC model — set 2026-10-15 with this workbook</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="33" customHeight="1">
-      <c r="A44" s="33" t="inlineStr"/>
-      <c r="B44" s="33" t="inlineStr">
+    <row r="53" ht="33" customHeight="1">
+      <c r="A53" s="33" t="inlineStr"/>
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>Must include</t>
         </is>
       </c>
-      <c r="C44" s="33" t="inlineStr">
+      <c r="C53" s="33" t="inlineStr">
         <is>
           <t>Both level determinations on one record · legitimate divergence between them · modifier 25</t>
         </is>
       </c>
-      <c r="D44" s="33" t="n"/>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="35" t="inlineStr">
+      <c r="D53" s="33" t="n"/>
+      <c r="E53" s="34" t="n"/>
+      <c r="F53" s="35" t="inlineStr">
         <is>
           <t>Not in the HC model — set 2026-10-15 with this workbook. Divergence is the reason single path is a specialty and not a view of the other two ED pools.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="39" customHeight="1">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="55" ht="52" customHeight="1">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>E/M is the one specialty whose parent dimension is NOT the HC Coverage Matrix category. The HC matrix splits it by level (35/40/25) and method (80/20), but the trainers' own breakdown spans AWV, TCM, chronic care management, telehealth and neonatal per-diem codes, none of which has a level. Service family is therefore the parent and the level and method splits are checked across the pool, exactly as Severity is on IP-DRG. The HC percentages are unchanged — only their position in the hierarchy is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="39" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>ED Facility, ED Profee and ED Single Path are three separate populations, not three views of one. The same encounter coded for the facility, coded professionally and coded single-path is three different charts; none of them belongs in the E/M pool, which is why the E/M dimension here has no ED setting. Confirmed 15 October 2026.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Severity on IP-DRG and Method on E/M are cross-cutting dimensions: a chart has a CC/MCC status and an MDM-or-time basis whatever its topic. They are checked across the pool, not decomposed per topic, which is why the topic sheets carry one dimension each.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="15" t="inlineStr">
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Where a target percentage here changes, the matching band row on the topic sheet and its child weights must change together. The band row's check cell is what tells you they have come apart.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A57:F57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2169,7 +2361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2270,73 +2462,73 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77" customHeight="1">
-      <c r="A7" s="24" t="n">
+    <row r="7" ht="99" customHeight="1">
+      <c r="A7" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>Add ED Profee, Surgery and ED Single Path to the HC model</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>Pools of 400, 300 and 300 were set here, outside the HC model. None of them has a +10% buffer calculation, a per-batch average, a batch count or a build-hour line. That is 1,000 charts the HC Specialty Grid, Chart Pool, FTE Demand and FTE Summary sheets do not know about — at HC's own build rates roughly 1,500 to 2,250 hours, close to a further FTE. Until they are added, the team size in that model is understated.</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Whoever owns the HC model</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="24" t="n">
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>E/M is classified by service family, not by the HC level split</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>Confirmed with the trainers on 2026-10-15. Their own breakdown of E/M spans annual wellness visits, transitional and chronic care management, telehealth, minor office procedures and neonatal per-diem critical care — none of which has an E/M level, so the HC matrix's level dimension cannot be the parent. Service family became the parent and the HC level (35/40/25) and method (80/20) splits are now checked across the pool rather than decomposed, the same treatment Severity gets on IP-DRG. No HC percentage changed; only its position in the hierarchy did.</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>Confirmed by the user</t>
+        </is>
+      </c>
+      <c r="E7" s="39" t="inlineStr">
+        <is>
+          <t>Settled 2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Set the cc_boundary flag policy for the 99285 / 99291 charts</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>Topic EDP-07 exists for charts where the critical care call is genuinely arguable, and the auditor module only plants against them when a trainer has set AnswerKey.cc_boundary to borderline. Without a policy on who sets it and on what evidence, the topic fills with charts nothing is ever planted in.</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>PL Trainer plus QR</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55" customHeight="1">
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>E/M priorities are set, including a fourth priority band</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>Level 3 and 4 office visits and the inpatient/observation trio are P1. Level 5 office, preventive and wellness, inpatient critical care and consultations are P2. Levels 1-2, minor procedures with an E/M, TCM, telehealth and NICU/PICU are P3. Chronic care management is P4, the first topic in the workbook to need a fourth band — real work, but the pool functions without it for a while.</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>Confirmed by the user</t>
+        </is>
+      </c>
+      <c r="E8" s="39" t="inlineStr">
+        <is>
+          <t>Settled 2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="77" customHeight="1">
       <c r="A9" s="24" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>Agree the constrained-supply topics</t>
+          <t>Add ED Profee, Surgery and ED Single Path to the HC model</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>IPD-13 (mental health), EDF-11 (behavioural health), IPD-16 (obstetric surgical) and IPD-24 (transplant) are narrowed by exclusion X2 or by case rarity. Each needs a stated floor below which it is reported as constrained rather than chased, so a gap report does not show a permanent red against a topic nobody can fill.</t>
+          <t>Pools of 400, 300 and 300 were set here, outside the HC model. None of them has a +10% buffer calculation, a per-batch average, a batch count or a build-hour line. That is 1,000 charts the HC Specialty Grid, Chart Pool, FTE Demand and FTE Summary sheets do not know about — at HC's own build rates roughly 1,500 to 2,250 hours, close to a further FTE. Until they are added, the team size in that model is understated.</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>PL Trainer plus Compliance for X2</t>
+          <t>Whoever owns the HC model</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -2345,23 +2537,23 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="44" customHeight="1">
+    <row r="10" ht="55" customHeight="1">
       <c r="A10" s="24" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>Decide how a topic-level gap report is produced</t>
+          <t>Set the cc_boundary flag policy for the 99285 / 99291 charts</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>Topic ID has to be a filterable field on the chart record for any of this to be measurable. HC section 9 sets the trigger at 80% of target reviewed monthly, which is not workable by hand across roughly 125 topics.</t>
+          <t>Topic EDP-07 exists for charts where the critical care call is genuinely arguable, and the auditor module only plants against them when a trainer has set AnswerKey.cc_boundary to borderline. Without a policy on who sets it and on what evidence, the topic fills with charts nothing is ever planted in.</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>PL Trainer plus the platform team</t>
+          <t>PL Trainer plus QR</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
@@ -2370,23 +2562,23 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="44" customHeight="1">
+    <row r="11" ht="55" customHeight="1">
       <c r="A11" s="24" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>Extend the topic layer to Denials/Edits and Ancillary</t>
+          <t>Agree the constrained-supply topics</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>Both are deferred from this pass. Their HC pools (165 and 594) and coverage matrices stand, so they are classified at category level but not at topic level — 759 charts, a quarter of the HC total, outside this framework.</t>
+          <t>IPD-13 (mental health), EDF-11 (behavioural health), IPD-16 (obstetric surgical) and IPD-24 (transplant) are narrowed by exclusion X2 or by case rarity. Each needs a stated floor below which it is reported as constrained rather than chased, so a gap report does not show a permanent red against a topic nobody can fill.</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>PL Trainer</t>
+          <t>PL Trainer plus Compliance for X2</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
@@ -2401,20 +2593,70 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
+          <t>Decide how a topic-level gap report is produced</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Topic ID has to be a filterable field on the chart record for any of this to be measurable. HC section 9 sets the trigger at 80% of target reviewed monthly, which is not workable by hand across roughly 125 topics.</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>PL Trainer plus the platform team</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Extend the topic layer to Denials/Edits and Ancillary</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Both are deferred from this pass. Their HC pools (165 and 594) and coverage matrices stand, so they are classified at category level but not at topic level — 759 charts, a quarter of the HC total, outside this framework.</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>PL Trainer</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
           <t>Confirm the difficulty skew per topic against real charts</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>The skew column is a judgement about what a topic can plausibly hold, made before any chart was sourced. Once a few hundred charts are classified and tiered, compare the actual tier distribution per topic against the skew and correct the column, not the charts.</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>PL Trainer, at the first refresh</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3128,7 +3370,7 @@
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>P1 — build first</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -3187,7 +3429,7 @@
       </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>P1 — build first</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -3246,7 +3488,7 @@
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>P1 — build first</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -3305,7 +3547,7 @@
       </c>
       <c r="H9" s="25" t="inlineStr">
         <is>
-          <t>P1 — build first</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -3832,7 +4074,7 @@
       </c>
       <c r="H18" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -3891,7 +4133,7 @@
       </c>
       <c r="H19" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -3961,7 +4203,7 @@
       </c>
       <c r="H21" s="25" t="inlineStr">
         <is>
-          <t>P1 — build first</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -4020,7 +4262,7 @@
       </c>
       <c r="H22" s="25" t="inlineStr">
         <is>
-          <t>P1 — build first</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -4429,7 +4671,7 @@
       </c>
       <c r="H29" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -4488,7 +4730,7 @@
       </c>
       <c r="H30" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -4547,7 +4789,7 @@
       </c>
       <c r="H31" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -4873,7 +5115,7 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -5414,7 +5656,7 @@
       </c>
       <c r="H18" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -5716,7 +5958,7 @@
       </c>
       <c r="H24" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -6616,7 +6858,7 @@
       </c>
       <c r="H21" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -6713,7 +6955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6753,7 +6995,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>COUNTA(A5:A24)-3</f>
+        <f>COUNTA(A5:A36)-9</f>
         <v/>
       </c>
       <c r="E2" s="17" t="inlineStr">
@@ -6762,7 +7004,7 @@
         </is>
       </c>
       <c r="F2" s="18">
-        <f>SUM(G5:G24)</f>
+        <f>SUM(G5:G36)</f>
         <v/>
       </c>
       <c r="G2" s="17" t="inlineStr">
@@ -6776,7 +7018,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Dimension: Level</t>
+          <t>Dimension: Service family</t>
         </is>
       </c>
     </row>
@@ -6852,15 +7094,15 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>LOW (LEVELS 2–3)  —  HC Coverage Matrix parent: 35%</t>
+          <t>OFFICE / OUTPATIENT VISITS  —  HC Coverage Matrix parent: 42%</t>
         </is>
       </c>
       <c r="F5" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$24,"Low (levels 2–3)",$F$5:$F$24),6)=0.35,"OK — topics sum to the 35% parent","CHECK — topics do not sum to the 35% parent")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1">
+        <f>IF(ROUND(SUMIF($B$5:$B$36,"Office / outpatient visits",$F$5:$F$36),6)=0.42,"OK — topics sum to the 42% parent","CHECK — topics do not sum to the 42% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
           <t>EM-01</t>
@@ -6868,34 +7110,34 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>Low (levels 2–3)</t>
+          <t>Office / outpatient visits</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>New patient office / outpatient, low (99202 / 99203)</t>
+          <t>Level 3 established patient office visit (99213)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>New-patient office visits with one self-limited or stable problem, minimal data, minimal-to-low risk.</t>
+          <t>Established-patient visits levelled at 3 on medical decision making: one stable chronic problem or a single acute uncomplicated one, limited data, low risk.</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>ED visits — ED Profee; established patients — EM-02</t>
+          <t>New patients — EM-03; level 4 — EM-02</t>
         </is>
       </c>
       <c r="F6" s="23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="24">
         <f>ROUND(F6*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H6" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -6910,16 +7152,16 @@
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t>New versus established determination, COPA, Data Review, Risk, the 2-of-3 rule</t>
+          <t>COPA for a stable chronic problem, Data Review, Risk, the 2-of-3 rule, diagnosis specificity</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>New-patient and established-patient office visits are separate ladders. The same level on the wrong ladder is the new-versus-established error, not a near miss.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1">
+          <t>With EM-02 this is the foundation of the whole specialty: the widest spread of complexity inside one code, which is what makes it the Week 1 workhorse. 99213 versus 99214 is the most common level error in outpatient coding, so carry charts that sit close to the line in both directions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="21" t="inlineStr">
         <is>
           <t>EM-02</t>
@@ -6927,58 +7169,58 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>Low (levels 2–3)</t>
+          <t>Office / outpatient visits</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>Established patient office / outpatient, low (99212 / 99213)</t>
+          <t>Level 4 established patient office visit (99214)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>Established-patient visits for stable chronic conditions or a single acute uncomplicated problem.</t>
+          <t>Established visits levelled at 4: two or more stable chronic conditions, or one with exacerbation, with prescription drug management or moderate risk.</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Level 5 — EM-05</t>
         </is>
       </c>
       <c r="F7" s="23" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="G7" s="24">
         <f>ROUND(F7*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H7" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
-          <t>Basic-led</t>
+          <t>Moderate-led</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
         <is>
-          <t>C8 Foundation</t>
+          <t>C1 High error rate</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t>COPA for a stable chronic condition, Data Review, Risk, the 2-of-3 rule</t>
+          <t>COPA, Data Review categories, Risk including prescription drug management, the 2-of-3 rule</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>The highest-volume topic in the specialty and the main Week 1 source. 99213 versus 99214 is the most common level error in outpatient coding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>The largest single topic in the pool. Vary the complexity deliberately — a 99214 earned on risk alone reads very differently from one earned on data, and a coder who has only seen the second will downcode the first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
         <is>
           <t>EM-03</t>
@@ -6986,34 +7228,34 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Low (levels 2–3)</t>
+          <t>Office / outpatient visits</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>Initial hospital / observation care, low (99221)</t>
+          <t>Level 3 new patient office visit (99203)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>First inpatient or observation encounter by the admitting provider at the lowest level of the ladder.</t>
+          <t>New-patient visits levelled at 3: a problem of low complexity, limited data, low risk.</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>ED-initiated observation — ED Profee (EDP-10)</t>
+          <t>Established patients — EM-01</t>
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G8" s="24">
         <f>ROUND(F8*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H8" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -7028,10 +7270,14 @@
       </c>
       <c r="K8" s="22" t="inlineStr">
         <is>
-          <t>Initial versus subsequent determination, COPA, Data Review, Risk, admission date rules</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr"/>
+          <t>New versus established determination, COPA, Data Review, Risk, the 2-of-3 rule</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>New-patient and established-patient office visits are separate ladders. Same level on the wrong ladder is the new-versus-established error, which is a different finding from a near miss on the right ladder.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="33" customHeight="1">
       <c r="A9" s="21" t="inlineStr">
@@ -7041,17 +7287,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Low (levels 2–3)</t>
+          <t>Office / outpatient visits</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>Subsequent hospital / observation care, low (99231)</t>
+          <t>Level 4 new patient office visit (99204)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>Daily inpatient visits where the patient is stable, recovering or improving.</t>
+          <t>New-patient visits levelled at 4: multiple problems or extensive data review with moderate risk.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -7060,35 +7306,35 @@
         </is>
       </c>
       <c r="F9" s="23" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G9" s="24">
         <f>ROUND(F9*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H9" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
-          <t>Basic-led</t>
+          <t>Moderate-led</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>C8 Foundation</t>
+          <t>C1 High error rate</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>Subsequent care ladder, interval history, COPA, Risk</t>
+          <t>COPA for multiple or chronic problems, independent interpretation and external discussion as data, moderate risk, the 2-of-3 rule</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>The inpatient ladder is distinct from both office ladders; a chart coded on the wrong ladder is a classifier error, not a level error.</t>
+          <t>The three-year rule decides new versus established and is the element most often taken on trust from the registration screen rather than the record.</t>
         </is>
       </c>
     </row>
@@ -7100,26 +7346,26 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Low (levels 2–3)</t>
+          <t>Office / outpatient visits</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>Preventive and annual wellness visits</t>
+          <t>Level 5 office visit, new and established (99205 / 99215)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>Preventive medicine services and the Medicare AWV, including a problem-oriented visit on the same day.</t>
+          <t>The top of both office ladders: high COPA, extensive data, high risk — severe exacerbation, threat to bodily function, or a decision for hospitalisation.</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Visits levelled by time rather than MDM — EM-07</t>
         </is>
       </c>
       <c r="F10" s="23" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G10" s="24">
         <f>ROUND(F10*$B$2,0)</f>
@@ -7132,92 +7378,96 @@
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
-          <t>Moderate-led</t>
+          <t>Complex-led</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
         <is>
-          <t>C7 Denial trends</t>
+          <t>C2 High dollar value</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>Age-banded preventive code selection, AWV versus preventive distinction, modifier 25 for a same-day problem visit, diagnosis linkage</t>
+          <t>COPA at the highest level, data categories including independent interpretation, high risk such as drug therapy requiring intensive monitoring, decision for hospitalisation</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>Not graded on medical decision making at all: applicable_weights drops the MDM weights for preventive charts, and sections_for_chart resolves the form per chart. A chart with no key keeps the full form, because absence is not evidence it is preventive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>MODERATE (LEVEL 4)  —  HC Coverage Matrix parent: 40%</t>
-        </is>
-      </c>
-      <c r="F11" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$24,"Moderate (level 4)",$F$5:$F$24),6)=0.4,"OK — topics sum to the 40% parent","CHECK — topics do not sum to the 40% parent")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="33" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
+          <t>Runs 10-15% of production and carries the highest office reimbursement, so an error here costs more than anywhere else on the ladder. Weighted at 7% rather than the production share because the pool exists to train the hard calls, not to mirror the mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>EM-06</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>Moderate (level 4)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>New patient office / outpatient, moderate (99204)</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>New-patient visits with multiple problems or extensive data review, moderate risk including prescription management.</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Office / outpatient visits</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Level 1-2 office visits (99202 / 99211 / 99212)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>The bottom of the ladders, including 99211 as the visit with no required provider evaluation.</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="23" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G12" s="24">
-        <f>ROUND(F12*$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>Moderate-led</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="inlineStr">
-        <is>
-          <t>C1 High error rate</t>
-        </is>
-      </c>
-      <c r="K12" s="22" t="inlineStr">
-        <is>
-          <t>COPA for multiple or chronic problems, data categories, prescription drug management as risk, the 2-of-3 rule</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr"/>
-    </row>
-    <row r="13" ht="33" customHeight="1">
+      <c r="F11" s="23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G11" s="24">
+        <f>ROUND(F11*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="27" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>Basic-led</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>C8 Foundation</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>Whether a billable E/M occurred at all, 99211 incident-to requirements, minimal COPA and risk</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>5-10% of production and deliberately held below that here: low error rate and low dollar value, so it earns a P3. Its real teaching value is the lower bound — sometimes the correct answer is that no E/M is billable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>TIME-BASED AND PROLONGED SERVICES  —  HC Coverage Matrix parent: 4%</t>
+        </is>
+      </c>
+      <c r="F12" s="20">
+        <f>IF(ROUND(SUMIF($B$5:$B$36,"Time-based and prolonged services",$F$5:$F$36),6)=0.04,"OK — topics sum to the 4% parent","CHECK — topics do not sum to the 4% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
         <is>
           <t>EM-07</t>
@@ -7225,17 +7475,17 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>Moderate (level 4)</t>
+          <t>Time-based and prolonged services</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>Established patient office / outpatient, moderate (99214)</t>
+          <t>Visits levelled by time, and prolonged service add-ons (99417 / G2212)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>The workhorse established visit: two or more stable chronic conditions, or one with exacerbation, with prescription management.</t>
+          <t>Visits where total time on the date of service decides the level rather than medical decision making, and the prolonged-service add-ons that attach to the highest level.</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -7244,7 +7494,7 @@
         </is>
       </c>
       <c r="F13" s="23" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="G13" s="24">
         <f>ROUND(F13*$B$2,0)</f>
@@ -7257,108 +7507,64 @@
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>Moderate-led</t>
+          <t>Complex-led</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
         <is>
-          <t>C1 High error rate</t>
+          <t>C7 Denial trends</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
         <is>
-          <t>COPA, Data Review, Risk, the 2-of-3 rule, chronic condition exacerbation documentation</t>
+          <t>What counts toward total time on the date of service, the time thresholds per code, add-on unit counting, MDM versus time as the basis</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>Largest single topic in the pool. Plant level errors in both directions here: upcoding is what payers audit for, downcoding is revenue quietly left behind.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
+          <t>These are the charts behind the HC Method split of 80% MDM and 20% time. Time-levelled visits are not graded on medical decision making at all, so applicable_weights drops the MDM weights and the form is resolved per chart. Deliberately a small share: the trainers asked for very few.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>PREVENTIVE AND WELLNESS  —  HC Coverage Matrix parent: 14%</t>
+        </is>
+      </c>
+      <c r="F14" s="20">
+        <f>IF(ROUND(SUMIF($B$5:$B$36,"Preventive and wellness",$F$5:$F$36),6)=0.14,"OK — topics sum to the 14% parent","CHECK — topics do not sum to the 14% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>EM-08</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>Moderate (level 4)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>Initial hospital / observation care, moderate (99222)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>Admissions with multiple active problems and moderate risk.</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="n">
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Preventive and wellness</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Annual wellness visit — initial versus subsequent (G0438 / G0439)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>The Medicare AWV and the determination that trips most often: G0438 is once per lifetime, G0439 every year after, and the Initial Preventive Physical Examination is a third thing again.</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Commercial preventive medicine visits — EM-09</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="n">
         <v>0.05</v>
-      </c>
-      <c r="G14" s="24">
-        <f>ROUND(F14*$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
-        <is>
-          <t>Moderate-led</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="inlineStr">
-        <is>
-          <t>C8 Foundation</t>
-        </is>
-      </c>
-      <c r="K14" s="22" t="inlineStr">
-        <is>
-          <t>COPA, data categories, risk of morbidity, initial versus subsequent</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="33" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>EM-09</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>Moderate (level 4)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>Subsequent hospital / observation care, moderate (99232)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>Daily visits where the patient is not responding adequately or has a minor complication.</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>0.06</v>
       </c>
       <c r="G15" s="24">
         <f>ROUND(F15*$B$2,0)</f>
@@ -7376,44 +7582,48 @@
       </c>
       <c r="J15" s="22" t="inlineStr">
         <is>
-          <t>C1 High error rate</t>
+          <t>C7 Denial trends</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
         <is>
-          <t>Subsequent care ladder, COPA for an inadequately responding problem, Data Review, Risk</t>
-        </is>
-      </c>
-      <c r="L15" s="11" t="inlineStr"/>
+          <t>Initial versus subsequent determination, the once-per-lifetime rule, IPPE versus AWV, required elements, diagnosis coding for a wellness visit</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>Billing G0438 for a patient who has had one before is a straight denial and a common one. The chart must carry enough history to make the determination answerable.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="33" customHeight="1">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>EM-10</t>
+          <t>EM-09</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>Moderate (level 4)</t>
+          <t>Preventive and wellness</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>Consultations, moderate (99243 / 99253)</t>
+          <t>Preventive medicine visits, age-banded (99381-99397)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>Office and inpatient consultations at moderate level, where the request and the reason for it must be documented.</t>
+          <t>Commercial preventive visits where the code is chosen by age band and by new versus established.</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Medicare AWV — EM-08</t>
         </is>
       </c>
       <c r="F16" s="23" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G16" s="24">
         <f>ROUND(F16*$B$2,0)</f>
@@ -7426,37 +7636,85 @@
       </c>
       <c r="I16" s="22" t="inlineStr">
         <is>
+          <t>Basic-led</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>C8 Foundation</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>Age-band code selection, new versus established, required components, diagnosis coding</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>Not graded on medical decision making: a preventive visit is off-ladder, so planting abstains and applicable_weights drops the MDM weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>EM-10</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Preventive and wellness</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Preventive or AWV with a same-day problem visit</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>A wellness or preventive visit where a problem was also addressed, so a separate E/M is reportable with modifier 25 — and the documentation has to support both.</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G17" s="24">
+        <f>ROUND(F17*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
-        <is>
-          <t>C6 Customer escalations</t>
-        </is>
-      </c>
-      <c r="K16" s="22" t="inlineStr">
-        <is>
-          <t>Consultation requirements (request, reason, report), consult versus transfer of care, COPA, Data Review, Risk</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>Consults are off-ladder for planting purposes: em_levels.py knows three ladders plus critical care, so a consult is not a near miss along any of them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>HIGH (LEVEL 5)  —  HC Coverage Matrix parent: 25%</t>
-        </is>
-      </c>
-      <c r="F17" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$24,"High (level 5)",$F$5:$F$24),6)=0.25,"OK — topics sum to the 25% parent","CHECK — topics do not sum to the 25% parent")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>C1 High error rate</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>Modifier 25 on the problem visit, splitting preventive from problem documentation, MDM for the problem portion only, patient liability consequence</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>The hardest preventive question and the one payers audit. Carry charts where the second E/M is NOT supported as well as charts where it is — a coder who always bills both is as wrong as one who never does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
           <t>EM-11</t>
@@ -7464,17 +7722,17 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>High (level 5)</t>
+          <t>Preventive and wellness</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>New patient office / outpatient, high (99205)</t>
+          <t>Screening and counselling services</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>New-patient visits with high COPA, extensive data and high risk.</t>
+          <t>Depression, obesity, alcohol misuse, smoking cessation and similar screening and behavioural counselling services, usually alongside another visit.</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -7483,7 +7741,7 @@
         </is>
       </c>
       <c r="F18" s="23" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G18" s="24">
         <f>ROUND(F18*$B$2,0)</f>
@@ -7496,205 +7754,125 @@
       </c>
       <c r="I18" s="22" t="inlineStr">
         <is>
-          <t>Complex-led</t>
+          <t>Moderate-led</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>C1 High error rate</t>
+          <t>C7 Denial trends</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>COPA at the highest level, independent interpretation and external discussion as data, high risk</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
+          <t>Service-specific code and G-code selection, time thresholds for counselling, frequency limits, diagnosis linkage, bundling against the visit</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>Frequency limits are the recurring denial: most of these have an annual or per-period cap and the record rarely states what was done before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>OFFICE PROCEDURES WITH AN E/M  —  HC Coverage Matrix parent: 5%</t>
+        </is>
+      </c>
+      <c r="F19" s="20">
+        <f>IF(ROUND(SUMIF($B$5:$B$36,"Office procedures with an E/M",$F$5:$F$36),6)=0.05,"OK — topics sum to the 5% parent","CHECK — topics do not sum to the 5% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="55" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>EM-12</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>High (level 5)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>Established patient office / outpatient, high (99215)</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>Established visits with severe exacerbation or threat to function, with high-risk management.</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Office procedures with an E/M</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Minor office procedures billed with an E/M</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>Cerumen removal, lesion destruction, skin tag removal, simple biopsies, injections and similar minor procedures performed at a visit.</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="23" t="n">
+      <c r="F20" s="23" t="n">
         <v>0.05</v>
-      </c>
-      <c r="G19" s="24">
-        <f>ROUND(F19*$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="H19" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>Complex-led</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="inlineStr">
-        <is>
-          <t>C1 High error rate</t>
-        </is>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
-        <is>
-          <t>COPA for severe exacerbation, data categories, high risk including drug therapy requiring monitoring</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>EM-13</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>High (level 5)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>Initial hospital / observation care, high (99223)</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>Admissions with high COPA and high risk of morbidity.</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="n">
-        <v>0.04</v>
       </c>
       <c r="G20" s="24">
         <f>ROUND(F20*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H20" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="H20" s="27" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
         <is>
-          <t>Complex-led</t>
+          <t>Moderate-led</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>C2 High dollar value</t>
+          <t>C1 High error rate</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>COPA, data categories, risk including decision for escalation of care</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>EM-14</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>High (level 5)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>Subsequent hospital / observation care, high (99233)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>Daily visits where the patient is unstable or has a significant complication.</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G21" s="24">
-        <f>ROUND(F21*$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="H21" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I21" s="22" t="inlineStr">
-        <is>
-          <t>Complex-led</t>
-        </is>
-      </c>
-      <c r="J21" s="22" t="inlineStr">
-        <is>
-          <t>C1 High error rate</t>
-        </is>
-      </c>
-      <c r="K21" s="22" t="inlineStr">
-        <is>
-          <t>COPA for an unstable problem, Data Review, Risk</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+          <t>Modifier 25 appropriateness, whether the E/M is separately identifiable from the procedure, procedure code selection by method and count, laterality and site</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>The whole topic is one question: was there a separately identifiable E/M, or is the visit the procedure? Cerumen removal needs instrumentation rather than lavage to be the procedure code at all, which is where it most often goes wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>CARE MANAGEMENT AND TRANSITIONAL CARE  —  HC Coverage Matrix parent: 5%</t>
+        </is>
+      </c>
+      <c r="F21" s="20">
+        <f>IF(ROUND(SUMIF($B$5:$B$36,"Care management and transitional care",$F$5:$F$36),6)=0.05,"OK — topics sum to the 5% parent","CHECK — topics do not sum to the 5% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>EM-15</t>
+          <t>EM-13</t>
         </is>
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>High (level 5)</t>
+          <t>Care management and transitional care</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>Consultations, high (99245 / 99255)</t>
+          <t>Transitional care management (99495 / 99496)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>Consultations at the highest level, typically multi-system or where the consultant assumes management.</t>
+          <t>TCM following a discharge: the interactive contact inside two business days, the face-to-face visit inside 7 or 14 days, and the MDM level that separates the two codes.</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -7711,7 +7889,7 @@
       </c>
       <c r="H22" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -7721,39 +7899,39 @@
       </c>
       <c r="J22" s="22" t="inlineStr">
         <is>
-          <t>C6 Customer escalations</t>
+          <t>C7 Denial trends</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
-          <t>Consultation requirements, COPA, data categories, high risk</t>
+          <t>Interactive contact timing, face-to-face visit window, moderate versus high MDM, the 30-day service period, what may not be billed alongside</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>Off-ladder; see EM-10.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="33" customHeight="1">
+          <t>Date arithmetic decides the code and the service period blocks other billing, so TCM is where a correct clinical read still produces a wrong claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>EM-16</t>
+          <t>EM-14</t>
         </is>
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>High (level 5)</t>
+          <t>Care management and transitional care</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>Discharge day management and prolonged services</t>
+          <t>Chronic care management (99490 / 99439 / 99487)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>Discharge day management by time, and prolonged service add-ons where total time drives the code.</t>
+          <t>CCM: the clinical staff time per calendar month, the care plan, consent, and the add-on codes for additional time.</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -7762,153 +7940,681 @@
         </is>
       </c>
       <c r="F23" s="23" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G23" s="24">
         <f>ROUND(F23*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H23" s="26" t="inlineStr">
+      <c r="H23" s="27" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>Moderate-led</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>C7 Denial trends</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>Time thresholds per calendar month, add-on unit counting, care plan and consent requirements, two chronic conditions, concurrent billing restrictions</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>Lowest priority in the specialty: real work, but the pool functions without it for a while. Time logs rather than clinical judgement, so it teaches a different skill from the rest of E/M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>TELEHEALTH  —  HC Coverage Matrix parent: 3%</t>
+        </is>
+      </c>
+      <c r="F24" s="20">
+        <f>IF(ROUND(SUMIF($B$5:$B$36,"Telehealth",$F$5:$F$36),6)=0.03,"OK — topics sum to the 3% parent","CHECK — topics do not sum to the 3% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="33" customHeight="1">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>EM-15</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Telehealth</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Telehealth and virtual services</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>Office visits delivered by telehealth, plus audio-only services, virtual check-ins and e-visits, where place of service and modifier decide payment.</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G25" s="24">
+        <f>ROUND(F25*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="27" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>Moderate-led</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>C6 Customer escalations</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>Place of service selection, telehealth modifiers (93, 95, FQ, FR), audio-only eligibility, time or MDM level, originating site</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>The rules move faster than any other part of E/M, so these charts date quickly. Tag the code-set version carefully and expect to refresh this topic every cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>INPATIENT AND OBSERVATION  —  HC Coverage Matrix parent: 18%</t>
+        </is>
+      </c>
+      <c r="F26" s="20">
+        <f>IF(ROUND(SUMIF($B$5:$B$36,"Inpatient and observation",$F$5:$F$36),6)=0.18,"OK — topics sum to the 18% parent","CHECK — topics do not sum to the 18% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="33" customHeight="1">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>EM-16</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Inpatient and observation</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Initial hospital inpatient or observation care (99221-99223)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>The first encounter by the admitting provider, levelled on MDM, including the merge of inpatient and observation into one code family.</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>ED-initiated observation by the ED physician — ED Profee (EDP-10)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G27" s="24">
+        <f>ROUND(F27*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>Moderate-led</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>C1 High error rate</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>Initial versus subsequent determination, COPA, Data Review, Risk, the admission date rule, inpatient and observation sharing one family</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>The inpatient ladder is distinct from both office ladders; a chart coded on the wrong ladder is a classifier error, not a level error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="33" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>EM-17</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Inpatient and observation</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Subsequent hospital inpatient or observation care (99231-99233)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>Daily visits, levelled by whether the patient is stable, responding inadequately, or unstable.</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G28" s="24">
+        <f>ROUND(F28*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>Moderate-led</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>C1 High error rate</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>Subsequent care level criteria, interval history, COPA for an inadequately responding problem, Risk</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>The highest-volume inpatient topic and where the level is most often defaulted to 99232 regardless of what the note supports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="33" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>EM-18</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Inpatient and observation</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>Discharge day management (99238 / 99239)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>Discharge services, where total time on the discharge date decides between the two codes.</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Same-day admit and discharge — EM-19</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G29" s="24">
+        <f>ROUND(F29*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>Moderate-led</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>C7 Denial trends</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>The 30-minute threshold, what counts toward discharge time, the discharge date rule, who may report it</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>Time-based rather than MDM-based. The documented time is frequently absent, in which case the lower code is the only defensible answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="33" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>EM-19</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Inpatient and observation</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Same-day admission and discharge (99234-99236)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>Encounters where the patient is admitted and discharged on the same calendar date, which is its own code family rather than an initial visit plus a discharge.</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G30" s="24">
+        <f>ROUND(F30*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="26" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>Moderate-led</t>
-        </is>
-      </c>
-      <c r="J23" s="22" t="inlineStr">
-        <is>
-          <t>C7 Denial trends</t>
-        </is>
-      </c>
-      <c r="K23" s="22" t="inlineStr">
-        <is>
-          <t>Time thresholds, what counts toward total time on the date of service, add-on code units, same-day rules</t>
-        </is>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>Time-based rather than MDM-based, so MDM weights do not apply. These are the charts behind the HC Method split of 80% MDM / 20% time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="33" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>EM-17</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>High (level 5)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>Split / shared visits and telehealth</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>Visits documented jointly by a physician and APP, and visits delivered by telehealth, where who may bill and at what level is the question.</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>Complex-led</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>C1 High error rate</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>Same-date criteria, the 8-hour rule, MDM level, why the initial-plus-discharge pairing is wrong here</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>Low volume and high error rate: coders reach for 99221 plus 99238 because that is what the encounter looks like.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>CRITICAL CARE AND NEONATAL INTENSIVE CARE  —  HC Coverage Matrix parent: 5%</t>
+        </is>
+      </c>
+      <c r="F31" s="20">
+        <f>IF(ROUND(SUMIF($B$5:$B$36,"Critical care and neonatal intensive care",$F$5:$F$36),6)=0.05,"OK — topics sum to the 5% parent","CHECK — topics do not sum to the 5% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="55" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>EM-20</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Critical care and neonatal intensive care</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Inpatient critical care (99291 / 99292)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Critical care delivered on the floor or in the ICU, with documented time, organ-system failure, and the bundled-service list.</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Critical care in the emergency department — ED Profee (EDP-08)</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G32" s="24">
+        <f>ROUND(F32*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>Complex-led</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>C2 High dollar value</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>Critical care qualification, time documentation and the 30-minute floor, bundled versus separately reportable procedures, same-day E/M by the same provider</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>Critical care sits outside every ladder in em_levels.py. This is the INPATIENT topic — ED critical care belongs to ED Profee, and the two must not share charts, because ED Facility, ED Profee, ED Single Path and E/M are four separate populations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>EM-21</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Critical care and neonatal intensive care</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>Neonatal and paediatric critical care (99468-99476)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>NICU and PICU per-diem critical care, where one code covers the calendar day and age bands decide the family.</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F33" s="23" t="n">
         <v>0.02</v>
       </c>
-      <c r="G24" s="24">
-        <f>ROUND(F24*$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="H24" s="27" t="inlineStr">
-        <is>
-          <t>P3 — build last</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="G33" s="24">
+        <f>ROUND(F33*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H33" s="27" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="J33" s="22" t="inlineStr">
         <is>
           <t>C6 Customer escalations</t>
         </is>
       </c>
-      <c r="K24" s="22" t="inlineStr">
-        <is>
-          <t>Substantive portion determination, modifier and place-of-service selection, telehealth modifier use, MDM or time level</t>
-        </is>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>Named in the HC coverage matrix as a must-include for this specialty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="K33" s="22" t="inlineStr">
+        <is>
+          <t>Per-diem versus time-based critical care, age band selection, initial versus subsequent day, what the per diem bundles</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>Per-diem coding is the opposite of everything else in this specialty — time does not accumulate and the day is the unit. Low volume, so it is the one P4 topic, but the per-diem logic is unlike anything else in the pool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>CONSULTATIONS  —  HC Coverage Matrix parent: 4%</t>
+        </is>
+      </c>
+      <c r="F34" s="20">
+        <f>IF(ROUND(SUMIF($B$5:$B$36,"Consultations",$F$5:$F$36),6)=0.04,"OK — topics sum to the 4% parent","CHECK — topics do not sum to the 4% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="55" customHeight="1">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>EM-22</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>Office and outpatient consultations (99242-99245)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>Outpatient consultations where the request, the reason for it and the report back must all be documented, and the payer must recognise consultation codes at all.</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G35" s="24">
+        <f>ROUND(F35*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H35" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>Complex-led</t>
+        </is>
+      </c>
+      <c r="J35" s="22" t="inlineStr">
+        <is>
+          <t>C6 Customer escalations</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>The three Rs (request, reason, report), consultation versus transfer of care, payer recognition, COPA, Data Review, Risk</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t>Consults are off-ladder for planting: em_levels.py knows three ladders plus critical care, so a consult level error is not a near miss along any of them. The commonest real error is billing a consult where care was simply transferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="33" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>EM-23</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Inpatient consultations (99252-99255)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>Inpatient and observation consultations, including the distinction from an initial hospital visit by a provider taking over care.</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Initial hospital care by the admitting provider — EM-16</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G36" s="24">
+        <f>ROUND(F36*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H36" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>Complex-led</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>C6 Customer escalations</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>The three Rs, consultant versus admitting provider, concurrent care documentation, MDM level</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>Two providers seeing the patient the same day is legitimate concurrent care, and the record has to show the different purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F25" s="29">
-        <f>SUM(F5:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="30">
-        <f>SUM(G5:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="F37" s="29">
+        <f>SUM(F5:F36)</f>
+        <v/>
+      </c>
+      <c r="G37" s="30">
+        <f>SUM(G5:G36)</f>
+        <v/>
+      </c>
+      <c r="H37" s="28" t="inlineStr">
         <is>
           <t>Weights must total 100%</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="39" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="39" ht="39" customHeight="1">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Shaded Topic %% cells are the only editable numbers on this sheet. Target charts recalculates from the pool on Specialty Summary. Edit a weight and the category check in its band row will read CHECK until the other weights in that category are rebalanced — the sheet is built to refuse a topic that quietly grows at its neighbours' expense.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Target charts is a ceiling, not a quota to fill at any cost. Where eligible supply genuinely is not there — a topic narrowed by exclusion X2, or a low-volume case type — report it as constrained in the gap review rather than substituting charts from an adjacent topic.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Variance in the strip above is rounding drift between the sum of topic targets and the pool. The pool is the authority.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="H25:L25"/>
-    <mergeCell ref="F17:L17"/>
-    <mergeCell ref="A25:E25"/>
+  <mergeCells count="25">
+    <mergeCell ref="F31:L31"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="F14:L14"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="F34:L34"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="F19:L19"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="F21:L21"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F12:L12"/>
+    <mergeCell ref="F24:L24"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="H37:L37"/>
+    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="F26:L26"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="F11:L11"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8580,7 +9286,7 @@
       </c>
       <c r="H16" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -8881,7 +9587,7 @@
       </c>
       <c r="H23" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -9668,7 +10374,7 @@
       </c>
       <c r="H15" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -9723,7 +10429,7 @@
       </c>
       <c r="H16" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -10509,7 +11215,7 @@
       </c>
       <c r="H18" s="27" t="inlineStr">
         <is>
-          <t>P3 — build last</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">

--- a/docs/PracticeLab_Chart_Composition_Taxonomy.xlsx
+++ b/docs/PracticeLab_Chart_Composition_Taxonomy.xlsx
@@ -4874,7 +4874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>COUNTA(A5:A24)-4</f>
+        <f>COUNTA(A5:A25)-4</f>
         <v/>
       </c>
       <c r="E2" s="17" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="F2" s="18">
-        <f>SUM(G5:G24)</f>
+        <f>SUM(G5:G25)</f>
         <v/>
       </c>
       <c r="G2" s="17" t="inlineStr">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="F5" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$24,"Levels 1–2",$F$5:$F$24),6)=0.2,"OK — topics sum to the 20% parent","CHECK — topics do not sum to the 20% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$25,"Levels 1–2",$F$5:$F$25),6)=0.2,"OK — topics sum to the 20% parent","CHECK — topics do not sum to the 20% parent")</f>
         <v/>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="F9" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$24,"Level 3",$F$5:$F$24),6)=0.3,"OK — topics sum to the 30% parent","CHECK — topics do not sum to the 30% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$25,"Level 3",$F$5:$F$25),6)=0.3,"OK — topics sum to the 30% parent","CHECK — topics do not sum to the 30% parent")</f>
         <v/>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Polytrauma — EDF-15</t>
+          <t>Polytrauma — EDF-16</t>
         </is>
       </c>
       <c r="F11" s="23" t="n">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="F14" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$24,"Level 4",$F$5:$F$24),6)=0.3,"OK — topics sum to the 30% parent","CHECK — topics do not sum to the 30% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$25,"Level 4",$F$5:$F$25),6)=0.3,"OK — topics sum to the 30% parent","CHECK — topics do not sum to the 30% parent")</f>
         <v/>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Intubated or critical care patients — EDF-13</t>
+          <t>Intubated or critical care patients — EDF-13 or EDF-14</t>
         </is>
       </c>
       <c r="F16" s="23" t="n">
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="F20" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$24,"Level 5 / critical care",$F$5:$F$24),6)=0.2,"OK — topics sum to the 20% parent","CHECK — topics do not sum to the 20% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$25,"Level 5 / critical care",$F$5:$F$25),6)=0.2,"OK — topics sum to the 20% parent","CHECK — topics do not sum to the 20% parent")</f>
         <v/>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>Patients with immediate threat requiring extensive evaluation and intervention, short of critical care time.</t>
+          <t>Patients with immediate threat requiring extensive evaluation and intervention, short of critical care.</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="F21" s="23" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G21" s="24">
         <f>ROUND(F21*$B$2,0)</f>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="L21" s="11" t="inlineStr"/>
     </row>
-    <row r="22" ht="44" customHeight="1">
+    <row r="22" ht="55" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
         <is>
           <t>EDF-14</t>
@@ -5823,16 +5823,16 @@
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>Encounters with documented critical care time and organ-system failure, including the bundled-service list.</t>
+          <t>Encounters with documented critical care time and organ-system failure, including the bundled-service list and the facility charge alongside it.</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Level 5 visits with no documented critical care time — EDF-13</t>
+          <t>Level 5 visits with no documented critical care time — EDF-13; arguable cases — EDF-15</t>
         </is>
       </c>
       <c r="F22" s="23" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="G22" s="24">
         <f>ROUND(F22*$B$2,0)</f>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
-          <t>Critical care qualification, time documentation, bundled versus separately reportable procedures, facility level interaction</t>
+          <t>Critical care qualification, time documentation, bundled versus separately reportable procedures, facility level interaction, revenue code use</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>Whether the condition qualifies as critical care at all is the hardest question in the ED. The time arithmetic is not the training point and is not where coders go wrong.</t>
+          <t>The largest critical care topic in any pool, because this is where the volume actually is. Whether the condition qualifies as critical care at all is the hardest question in the ED; the time arithmetic is not the training point and critical care time is never planted.</t>
         </is>
       </c>
     </row>
@@ -5877,21 +5877,21 @@
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>Trauma activation</t>
+          <t>The level 5 versus critical care boundary</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>Encounters meeting the trauma team activation criteria, with the activation charge and its documentation requirements.</t>
+          <t>Facility encounters sitting on the line: high-acuity patients where whether critical care was delivered at all is genuinely arguable on the record.</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Clear-cut critical care — EDF-14; clear-cut level 5 — EDF-13</t>
         </is>
       </c>
       <c r="F23" s="23" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G23" s="24">
         <f>ROUND(F23*$B$2,0)</f>
@@ -5909,21 +5909,21 @@
       </c>
       <c r="J23" s="22" t="inlineStr">
         <is>
-          <t>C7 Denial trends</t>
+          <t>C6 Customer escalations</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
         <is>
-          <t>Trauma activation criteria and pre-notification requirement, revenue code use, injury coding, facility level</t>
+          <t>Critical care qualification against the facility acuity tool, organ system failure, what the record must show, the resulting facility level</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>The activation charge requires pre-hospital notification; charts missing it teach the denial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+          <t>The facility-side twin of EDP-07. A generated error cannot invent this call, so these charts earn their place by being argued rather than planted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="33" customHeight="1">
       <c r="A24" s="21" t="inlineStr">
         <is>
           <t>EDF-16</t>
@@ -5936,12 +5936,12 @@
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>Cardiac arrest and resuscitation</t>
+          <t>Trauma activation</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>Resuscitation encounters including CPR, defibrillation, intubation and death in the department.</t>
+          <t>Encounters meeting the trauma team activation criteria, with the activation charge and its documentation requirements.</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -5956,64 +5956,127 @@
         <f>ROUND(F24*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H24" s="27" t="inlineStr">
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>Complex-led</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>C7 Denial trends</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>Trauma activation criteria and pre-notification requirement, revenue code use, injury coding, facility level</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>The activation charge requires pre-hospital notification; charts missing it teach the denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="33" customHeight="1">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>EDF-17</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Level 5 / critical care</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Cardiac arrest and resuscitation</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>Resuscitation encounters including CPR, defibrillation, intubation and death in the department.</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G25" s="24">
+        <f>ROUND(F25*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="27" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>C2 High dollar value</t>
         </is>
       </c>
-      <c r="K24" s="22" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>Resuscitation procedure coding, critical care interaction, disposition including expired, diagnosis sequencing</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>Resuscitation and critical care are reported together more often than not, so this topic is read alongside EDF-14 rather than instead of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F25" s="29">
-        <f>SUM(F5:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="30">
-        <f>SUM(G5:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="F26" s="29">
+        <f>SUM(F5:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="30">
+        <f>SUM(G5:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="28" t="inlineStr">
         <is>
           <t>Weights must total 100%</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="39" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="28" ht="39" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Shaded Topic %% cells are the only editable numbers on this sheet. Target charts recalculates from the pool on Specialty Summary. Edit a weight and the category check in its band row will read CHECK until the other weights in that category are rebalanced — the sheet is built to refuse a topic that quietly grows at its neighbours' expense.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Target charts is a ceiling, not a quota to fill at any cost. Where eligible supply genuinely is not there — a topic narrowed by exclusion X2, or a low-volume case type — report it as constrained in the gap review rather than substituting charts from an adjacent topic.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Variance in the strip above is rounding drift between the sum of topic targets and the pool. The pool is the authority.</t>
         </is>
@@ -6021,14 +6084,14 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="H26:L26"/>
     <mergeCell ref="F14:L14"/>
     <mergeCell ref="A29:L29"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="H25:L25"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="F9:L9"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="F9:L9"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="F20:L20"/>
@@ -6047,7 +6110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6087,7 +6150,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>COUNTA(A5:A21)-6</f>
+        <f>COUNTA(A5:A22)-6</f>
         <v/>
       </c>
       <c r="E2" s="17" t="inlineStr">
@@ -6096,7 +6159,7 @@
         </is>
       </c>
       <c r="F2" s="18">
-        <f>SUM(G5:G21)</f>
+        <f>SUM(G5:G22)</f>
         <v/>
       </c>
       <c r="G2" s="17" t="inlineStr">
@@ -6186,11 +6249,11 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>LOW ACUITY  —  HC Coverage Matrix parent: 8%</t>
+          <t>LOW ACUITY  —  HC Coverage Matrix parent: 7%</t>
         </is>
       </c>
       <c r="F5" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$21,"Low acuity",$F$5:$F$21),6)=0.08,"OK — topics sum to the 8% parent","CHECK — topics do not sum to the 8% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$22,"Low acuity",$F$5:$F$22),6)=0.07,"OK — topics sum to the 7% parent","CHECK — topics do not sum to the 7% parent")</f>
         <v/>
       </c>
     </row>
@@ -6221,7 +6284,7 @@
         </is>
       </c>
       <c r="F6" s="23" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G6" s="24">
         <f>ROUND(F6*$B$2,0)</f>
@@ -6256,11 +6319,11 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>MODERATE  —  HC Coverage Matrix parent: 18%</t>
+          <t>MODERATE  —  HC Coverage Matrix parent: 16%</t>
         </is>
       </c>
       <c r="F7" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$21,"Moderate",$F$5:$F$21),6)=0.18,"OK — topics sum to the 18% parent","CHECK — topics do not sum to the 18% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$22,"Moderate",$F$5:$F$22),6)=0.16,"OK — topics sum to the 16% parent","CHECK — topics do not sum to the 16% parent")</f>
         <v/>
       </c>
     </row>
@@ -6291,7 +6354,7 @@
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="24">
         <f>ROUND(F8*$B$2,0)</f>
@@ -6385,11 +6448,11 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>LEVEL 4  —  HC Coverage Matrix parent: 20%</t>
+          <t>LEVEL 4  —  HC Coverage Matrix parent: 18%</t>
         </is>
       </c>
       <c r="F10" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$21,"Level 4",$F$5:$F$21),6)=0.2,"OK — topics sum to the 20% parent","CHECK — topics do not sum to the 20% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$22,"Level 4",$F$5:$F$22),6)=0.18,"OK — topics sum to the 18% parent","CHECK — topics do not sum to the 18% parent")</f>
         <v/>
       </c>
     </row>
@@ -6420,7 +6483,7 @@
         </is>
       </c>
       <c r="F11" s="23" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G11" s="24">
         <f>ROUND(F11*$B$2,0)</f>
@@ -6479,7 +6542,7 @@
         </is>
       </c>
       <c r="F12" s="23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="G12" s="24">
         <f>ROUND(F12*$B$2,0)</f>
@@ -6510,11 +6573,11 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>LEVEL 5  —  HC Coverage Matrix parent: 24%</t>
+          <t>LEVEL 5  —  HC Coverage Matrix parent: 21%</t>
         </is>
       </c>
       <c r="F13" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$21,"Level 5",$F$5:$F$21),6)=0.24,"OK — topics sum to the 24% parent","CHECK — topics do not sum to the 24% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$22,"Level 5",$F$5:$F$22),6)=0.21,"OK — topics sum to the 21% parent","CHECK — topics do not sum to the 21% parent")</f>
         <v/>
       </c>
     </row>
@@ -6545,7 +6608,7 @@
         </is>
       </c>
       <c r="F14" s="23" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="G14" s="24">
         <f>ROUND(F14*$B$2,0)</f>
@@ -6600,7 +6663,7 @@
         </is>
       </c>
       <c r="F15" s="23" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G15" s="24">
         <f>ROUND(F15*$B$2,0)</f>
@@ -6635,15 +6698,15 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>CRITICAL CARE  —  HC Coverage Matrix parent: 12%</t>
+          <t>CRITICAL CARE  —  HC Coverage Matrix parent: 20%</t>
         </is>
       </c>
       <c r="F16" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$21,"Critical care",$F$5:$F$21),6)=0.12,"OK — topics sum to the 12% parent","CHECK — topics do not sum to the 12% parent")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
+        <f>IF(ROUND(SUMIF($B$5:$B$22,"Critical care",$F$5:$F$22),6)=0.2,"OK — topics sum to the 20% parent","CHECK — topics do not sum to the 20% parent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="55" customHeight="1">
       <c r="A17" s="21" t="inlineStr">
         <is>
           <t>EDP-08</t>
@@ -6666,11 +6729,11 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Critical care delivered on the floor or in the ICU — E/M (EM-20)</t>
         </is>
       </c>
       <c r="F17" s="23" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="G17" s="24">
         <f>ROUND(F17*$B$2,0)</f>
@@ -6693,80 +6756,84 @@
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
-          <t>Critical care qualification, bundled procedures, separately reportable procedures, diagnosis sequencing</t>
+          <t>Critical care qualification, bundled procedures, diagnosis sequencing, same-day E/M by the same provider</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>The 99292 unit count follows from the time and is not where coders go wrong; critical care time itself is never planted. An auditor validates the code, not the arithmetic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+          <t>The second largest critical care topic after EDF-14, and weighted for the volume the ED actually sees. The 99292 unit count follows from the time and is not where coders go wrong; critical care time itself is never planted. An auditor validates the code, not the arithmetic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>EDP-09</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Critical care</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Critical care with separately reportable procedures</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Critical care encounters where a procedure outside the bundled list was performed — central line, chest tube, intubation, transvenous pacing.</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Procedures already bundled into critical care — EDP-08</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G18" s="24">
+        <f>ROUND(F18*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>Complex-led</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>C2 High dollar value</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>Which procedures the critical care code bundles and which it does not, modifier 25 and 59, procedure code selection, time excluded for separately reported work</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>The bundled list is the whole question, and time spent on a separately reportable procedure cannot also count toward critical care time — a double-count coders make routinely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>CROSS-CUTTING  —  HC Coverage Matrix parent: 18%</t>
         </is>
       </c>
-      <c r="F18" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$21,"Cross-cutting",$F$5:$F$21),6)=0.18,"OK — topics sum to the 18% parent","CHECK — topics do not sum to the 18% parent")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>EDP-09</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>Cross-cutting</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>ED procedures billed with an E/M</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>Laceration repair, I&amp;D, fracture care, joint reduction and foreign body removal alongside the ED E/M.</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G19" s="24">
-        <f>ROUND(F19*$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="H19" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>Moderate-led</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="inlineStr">
-        <is>
-          <t>C1 High error rate</t>
-        </is>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
-        <is>
-          <t>Procedure code selection, modifier 25 and 59, bundling against the E/M, laterality and site</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr"/>
+      <c r="F19" s="20">
+        <f>IF(ROUND(SUMIF($B$5:$B$22,"Cross-cutting",$F$5:$F$22),6)=0.18,"OK — topics sum to the 18% parent","CHECK — topics do not sum to the 18% parent")</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="21" t="inlineStr">
@@ -6781,12 +6848,12 @@
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>Observation and admission by the ED physician</t>
+          <t>ED procedures billed with an E/M</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>Encounters where the ED physician initiates observation or admits, and the service crosses code families.</t>
+          <t>Laceration repair, I&amp;D, fracture care, joint reduction and foreign body removal alongside the ED E/M.</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -6795,7 +6862,7 @@
         </is>
       </c>
       <c r="F20" s="23" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="G20" s="24">
         <f>ROUND(F20*$B$2,0)</f>
@@ -6808,22 +6875,22 @@
       </c>
       <c r="I20" s="22" t="inlineStr">
         <is>
-          <t>Complex-led</t>
+          <t>Moderate-led</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>C7 Denial trends</t>
+          <t>C1 High error rate</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>Which code family applies, same-day E/M rules, modifier 25, diagnosis supporting the status</t>
+          <t>Procedure code selection, modifier 25 and 59, bundling against the E/M, laterality and site</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr"/>
     </row>
-    <row r="21" ht="33" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="21" t="inlineStr">
         <is>
           <t>EDP-11</t>
@@ -6836,12 +6903,12 @@
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>Split / shared and teaching-physician documentation</t>
+          <t>Observation and admission by the ED physician</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>Encounters documented by a resident, APP or jointly, where attestation and substantive-portion rules decide what is billable.</t>
+          <t>Encounters where the ED physician initiates observation or admits, and the service crosses code families.</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -6856,68 +6923,123 @@
         <f>ROUND(F21*$B$2,0)</f>
         <v/>
       </c>
-      <c r="H21" s="27" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>Complex-led</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>C7 Denial trends</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>Which code family applies, same-day E/M rules, modifier 25, diagnosis supporting the status</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="33" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>EDP-12</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Split / shared and teaching-physician documentation</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Encounters documented by a resident, APP or jointly, where attestation and substantive-portion rules decide what is billable.</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G22" s="24">
+        <f>ROUND(F22*$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>Complex-led</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>C6 Customer escalations</t>
         </is>
       </c>
-      <c r="K21" s="22" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>Split/shared substantive portion, teaching physician attestation, modifier use, MDM level</t>
         </is>
       </c>
-      <c r="L21" s="11" t="inlineStr">
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>A documentation-rule topic rather than a code-selection one: the correct answer sometimes is that the service is not billable as documented.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F22" s="29">
-        <f>SUM(F5:F21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="30">
-        <f>SUM(G5:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="F23" s="29">
+        <f>SUM(F5:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="30">
+        <f>SUM(G5:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="28" t="inlineStr">
         <is>
           <t>Weights must total 100%</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="39" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
+    <row r="25" ht="39" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Shaded Topic %% cells are the only editable numbers on this sheet. Target charts recalculates from the pool on Specialty Summary. Edit a weight and the category check in its band row will read CHECK until the other weights in that category are rebalanced — the sheet is built to refuse a topic that quietly grows at its neighbours' expense.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Target charts is a ceiling, not a quota to fill at any cost. Where eligible supply genuinely is not there — a topic narrowed by exclusion X2, or a low-volume case type — report it as constrained in the gap review rather than substituting charts from an adjacent topic.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Variance in the strip above is rounding drift between the sum of topic targets and the pool. The pool is the authority.</t>
         </is>
@@ -6927,23 +7049,23 @@
   <mergeCells count="19">
     <mergeCell ref="F13:L13"/>
     <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A26:L26"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="I2:L2"/>
     <mergeCell ref="F10:L10"/>
     <mergeCell ref="F16:L16"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="F19:L19"/>
     <mergeCell ref="F7:L7"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="H22:L22"/>
+    <mergeCell ref="A23:E23"/>
     <mergeCell ref="F5:L5"/>
-    <mergeCell ref="F18:L18"/>
-    <mergeCell ref="A24:L24"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="H23:L23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8076,7 +8198,7 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>ED-initiated observation by the ED physician — ED Profee (EDP-10)</t>
+          <t>ED-initiated observation by the ED physician — ED Profee (EDP-11)</t>
         </is>
       </c>
       <c r="F27" s="23" t="n">
@@ -10712,11 +10834,11 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>LOW ACUITY  —  HC Coverage Matrix parent: 8%</t>
+          <t>LOW ACUITY  —  HC Coverage Matrix parent: 7%</t>
         </is>
       </c>
       <c r="F5" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$18,"Low acuity",$F$5:$F$18),6)=0.08,"OK — topics sum to the 8% parent","CHECK — topics do not sum to the 8% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$18,"Low acuity",$F$5:$F$18),6)=0.07,"OK — topics sum to the 7% parent","CHECK — topics do not sum to the 7% parent")</f>
         <v/>
       </c>
     </row>
@@ -10747,7 +10869,7 @@
         </is>
       </c>
       <c r="F6" s="23" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G6" s="24">
         <f>ROUND(F6*$B$2,0)</f>
@@ -10782,11 +10904,11 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>MODERATE  —  HC Coverage Matrix parent: 18%</t>
+          <t>MODERATE  —  HC Coverage Matrix parent: 16%</t>
         </is>
       </c>
       <c r="F7" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$18,"Moderate",$F$5:$F$18),6)=0.18,"OK — topics sum to the 18% parent","CHECK — topics do not sum to the 18% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$18,"Moderate",$F$5:$F$18),6)=0.16,"OK — topics sum to the 16% parent","CHECK — topics do not sum to the 16% parent")</f>
         <v/>
       </c>
     </row>
@@ -10817,7 +10939,7 @@
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="G8" s="24">
         <f>ROUND(F8*$B$2,0)</f>
@@ -10852,11 +10974,11 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>LEVEL 4  —  HC Coverage Matrix parent: 20%</t>
+          <t>LEVEL 4  —  HC Coverage Matrix parent: 18%</t>
         </is>
       </c>
       <c r="F9" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$18,"Level 4",$F$5:$F$18),6)=0.2,"OK — topics sum to the 20% parent","CHECK — topics do not sum to the 20% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$18,"Level 4",$F$5:$F$18),6)=0.18,"OK — topics sum to the 18% parent","CHECK — topics do not sum to the 18% parent")</f>
         <v/>
       </c>
     </row>
@@ -10887,7 +11009,7 @@
         </is>
       </c>
       <c r="F10" s="23" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G10" s="24">
         <f>ROUND(F10*$B$2,0)</f>
@@ -10922,11 +11044,11 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>LEVEL 5  —  HC Coverage Matrix parent: 22%</t>
+          <t>LEVEL 5  —  HC Coverage Matrix parent: 21%</t>
         </is>
       </c>
       <c r="F11" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$18,"Level 5",$F$5:$F$18),6)=0.22,"OK — topics sum to the 22% parent","CHECK — topics do not sum to the 22% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$18,"Level 5",$F$5:$F$18),6)=0.21,"OK — topics sum to the 21% parent","CHECK — topics do not sum to the 21% parent")</f>
         <v/>
       </c>
     </row>
@@ -10957,7 +11079,7 @@
         </is>
       </c>
       <c r="F12" s="23" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G12" s="24">
         <f>ROUND(F12*$B$2,0)</f>
@@ -10992,11 +11114,11 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>CRITICAL CARE  —  HC Coverage Matrix parent: 12%</t>
+          <t>CRITICAL CARE  —  HC Coverage Matrix parent: 18%</t>
         </is>
       </c>
       <c r="F13" s="20">
-        <f>IF(ROUND(SUMIF($B$5:$B$18,"Critical care",$F$5:$F$18),6)=0.12,"OK — topics sum to the 12% parent","CHECK — topics do not sum to the 12% parent")</f>
+        <f>IF(ROUND(SUMIF($B$5:$B$18,"Critical care",$F$5:$F$18),6)=0.18,"OK — topics sum to the 18% parent","CHECK — topics do not sum to the 18% parent")</f>
         <v/>
       </c>
     </row>
@@ -11027,7 +11149,7 @@
         </is>
       </c>
       <c r="F14" s="23" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G14" s="24">
         <f>ROUND(F14*$B$2,0)</f>

--- a/docs/PracticeLab_Chart_Composition_Taxonomy.xlsx
+++ b/docs/PracticeLab_Chart_Composition_Taxonomy.xlsx
@@ -647,7 +647,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Inventory classification for chart identification and sourcing · built 15 October 2026</t>
+          <t>Inventory classification for chart identification and sourcing · built 21 October 2026</t>
         </is>
       </c>
     </row>
